--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12712" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15890" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>
@@ -25456,2532 +25456,2532 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>7381</v>
+        <v>7913</v>
       </c>
       <c r="B1" t="s">
-        <v>7400</v>
+        <v>7932</v>
       </c>
       <c r="C1" t="s">
         <v>7401</v>
       </c>
       <c r="D1" t="s">
-        <v>7424</v>
+        <v>7985</v>
       </c>
       <c r="E1" t="s">
         <v>7439</v>
       </c>
       <c r="F1" t="s">
-        <v>7443</v>
+        <v>7933</v>
       </c>
       <c r="G1" t="s">
-        <v>7462</v>
+        <v>7950</v>
       </c>
       <c r="H1" t="s">
-        <v>7477</v>
+        <v>7970</v>
       </c>
       <c r="I1" t="s">
-        <v>7495</v>
+        <v>7991</v>
       </c>
       <c r="J1" t="s">
-        <v>7515</v>
+        <v>8011</v>
       </c>
       <c r="K1" t="s">
         <v>7537</v>
       </c>
       <c r="L1" t="s">
-        <v>7539</v>
+        <v>8039</v>
       </c>
       <c r="M1" t="s">
-        <v>7541</v>
+        <v>8045</v>
       </c>
       <c r="N1" t="s">
-        <v>7561</v>
+        <v>8065</v>
       </c>
       <c r="O1" t="s">
-        <v>7563</v>
+        <v>8071</v>
       </c>
       <c r="P1" t="s">
-        <v>7586</v>
+        <v>8094</v>
       </c>
       <c r="Q1" t="s">
-        <v>7607</v>
+        <v>8115</v>
       </c>
       <c r="R1" t="s">
-        <v>7629</v>
+        <v>8137</v>
       </c>
       <c r="S1" t="s">
-        <v>7652</v>
+        <v>8160</v>
       </c>
       <c r="T1" t="s">
-        <v>7675</v>
+        <v>8183</v>
       </c>
       <c r="U1" t="s">
-        <v>7683</v>
+        <v>8194</v>
       </c>
       <c r="V1" t="s">
-        <v>7685</v>
+        <v>8200</v>
       </c>
       <c r="W1" t="s">
-        <v>7705</v>
+        <v>8220</v>
       </c>
       <c r="X1" t="s">
-        <v>7725</v>
+        <v>8240</v>
       </c>
       <c r="Y1" t="s">
-        <v>7747</v>
+        <v>8262</v>
       </c>
       <c r="Z1" t="s">
-        <v>7769</v>
+        <v>8284</v>
       </c>
       <c r="AA1" t="s">
-        <v>7791</v>
+        <v>8306</v>
       </c>
       <c r="AB1" t="s">
-        <v>7814</v>
+        <v>8329</v>
       </c>
       <c r="AC1" t="s">
-        <v>7834</v>
+        <v>8350</v>
       </c>
       <c r="AD1" t="s">
-        <v>7836</v>
+        <v>8356</v>
       </c>
       <c r="AE1" t="s">
-        <v>7838</v>
+        <v>8362</v>
       </c>
       <c r="AF1" t="s">
-        <v>7861</v>
+        <v>8385</v>
       </c>
       <c r="AG1" t="s">
-        <v>7884</v>
+        <v>8408</v>
       </c>
       <c r="AH1" t="s">
         <v>7886</v>
       </c>
       <c r="AI1" t="s">
-        <v>7909</v>
+        <v>8460</v>
       </c>
       <c r="AJ1" t="s">
-        <v>7911</v>
+        <v>8462</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7382</v>
+        <v>7914</v>
       </c>
       <c r="B2" s="1">
         <v>2012</v>
       </c>
       <c r="C2" t="s">
-        <v>7402</v>
+        <v>8459</v>
       </c>
       <c r="D2" t="s">
-        <v>7425</v>
+        <v>8459</v>
       </c>
       <c r="E2" t="s">
-        <v>7440</v>
+        <v>8463</v>
       </c>
       <c r="F2" t="s">
-        <v>7444</v>
+        <v>8459</v>
       </c>
       <c r="G2" t="s">
-        <v>7463</v>
+        <v>8463</v>
       </c>
       <c r="H2" t="s">
-        <v>7478</v>
+        <v>8459</v>
       </c>
       <c r="I2" t="s">
-        <v>7496</v>
+        <v>8459</v>
       </c>
       <c r="J2" t="s">
-        <v>7516</v>
+        <v>8459</v>
       </c>
       <c r="K2" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L2" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M2" t="s">
-        <v>7542</v>
+        <v>8459</v>
       </c>
       <c r="N2" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O2" t="s">
-        <v>7564</v>
+        <v>8459</v>
       </c>
       <c r="P2" t="s">
-        <v>7587</v>
+        <v>8459</v>
       </c>
       <c r="Q2" t="s">
-        <v>7608</v>
+        <v>8459</v>
       </c>
       <c r="R2" t="s">
-        <v>7630</v>
+        <v>8459</v>
       </c>
       <c r="S2" t="s">
-        <v>7653</v>
+        <v>8459</v>
       </c>
       <c r="T2" t="s">
-        <v>7676</v>
+        <v>8463</v>
       </c>
       <c r="U2" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V2" t="s">
-        <v>7686</v>
+        <v>8459</v>
       </c>
       <c r="W2" t="s">
-        <v>7706</v>
+        <v>8459</v>
       </c>
       <c r="X2" t="s">
-        <v>7726</v>
+        <v>8459</v>
       </c>
       <c r="Y2" t="s">
-        <v>7748</v>
+        <v>8459</v>
       </c>
       <c r="Z2" t="s">
-        <v>7770</v>
+        <v>8459</v>
       </c>
       <c r="AA2" t="s">
-        <v>7792</v>
+        <v>8459</v>
       </c>
       <c r="AB2" t="s">
-        <v>7815</v>
+        <v>8459</v>
       </c>
       <c r="AC2" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD2" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE2" t="s">
-        <v>7839</v>
+        <v>8459</v>
       </c>
       <c r="AF2" t="s">
-        <v>7862</v>
+        <v>8459</v>
       </c>
       <c r="AG2" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH2" t="s">
-        <v>7887</v>
+        <v>8459</v>
       </c>
       <c r="AI2" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ2" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7383</v>
+        <v>7915</v>
       </c>
       <c r="B3" s="1">
         <v>2009</v>
       </c>
       <c r="C3" t="s">
-        <v>7403</v>
+        <v>8459</v>
       </c>
       <c r="D3" t="s">
-        <v>7426</v>
+        <v>8459</v>
       </c>
       <c r="E3" t="s">
-        <v>7441</v>
+        <v>8459</v>
       </c>
       <c r="F3" t="s">
-        <v>7445</v>
+        <v>8459</v>
       </c>
       <c r="G3" t="s">
-        <v>7464</v>
+        <v>8459</v>
       </c>
       <c r="H3" t="s">
-        <v>7479</v>
+        <v>8459</v>
       </c>
       <c r="I3" t="s">
-        <v>7497</v>
+        <v>8459</v>
       </c>
       <c r="J3" t="s">
-        <v>7517</v>
+        <v>8459</v>
       </c>
       <c r="K3" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L3" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M3" t="s">
-        <v>7543</v>
+        <v>8459</v>
       </c>
       <c r="N3" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O3" t="s">
-        <v>7565</v>
+        <v>8459</v>
       </c>
       <c r="P3" t="s">
-        <v>7588</v>
+        <v>8459</v>
       </c>
       <c r="Q3" t="s">
-        <v>7609</v>
+        <v>8459</v>
       </c>
       <c r="R3" t="s">
-        <v>7631</v>
+        <v>8459</v>
       </c>
       <c r="S3" t="s">
-        <v>7654</v>
+        <v>8459</v>
       </c>
       <c r="T3" t="s">
-        <v>7676</v>
+        <v>8463</v>
       </c>
       <c r="U3" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V3" t="s">
-        <v>7687</v>
+        <v>8459</v>
       </c>
       <c r="W3" t="s">
-        <v>7707</v>
+        <v>8459</v>
       </c>
       <c r="X3" t="s">
-        <v>7727</v>
+        <v>8459</v>
       </c>
       <c r="Y3" t="s">
-        <v>7749</v>
+        <v>8459</v>
       </c>
       <c r="Z3" t="s">
-        <v>7771</v>
+        <v>8459</v>
       </c>
       <c r="AA3" t="s">
-        <v>7793</v>
+        <v>8459</v>
       </c>
       <c r="AB3" t="s">
-        <v>7816</v>
+        <v>8459</v>
       </c>
       <c r="AC3" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD3" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE3" t="s">
-        <v>7840</v>
+        <v>8459</v>
       </c>
       <c r="AF3" t="s">
-        <v>7863</v>
+        <v>8459</v>
       </c>
       <c r="AG3" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH3" t="s">
-        <v>7888</v>
+        <v>8459</v>
       </c>
       <c r="AI3" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ3" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7384</v>
+        <v>7916</v>
       </c>
       <c r="B4" s="1">
         <v>2008</v>
       </c>
       <c r="C4" t="s">
-        <v>7404</v>
+        <v>8459</v>
       </c>
       <c r="D4" t="s">
-        <v>7427</v>
+        <v>8463</v>
       </c>
       <c r="E4" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F4" t="s">
-        <v>7446</v>
+        <v>8463</v>
       </c>
       <c r="G4" t="s">
-        <v>7465</v>
+        <v>8463</v>
       </c>
       <c r="H4" t="s">
-        <v>7480</v>
+        <v>8463</v>
       </c>
       <c r="I4" t="s">
-        <v>7498</v>
+        <v>8463</v>
       </c>
       <c r="J4" t="s">
-        <v>7518</v>
+        <v>8463</v>
       </c>
       <c r="K4" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L4" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M4" t="s">
-        <v>7544</v>
+        <v>8463</v>
       </c>
       <c r="N4" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O4" t="s">
-        <v>7566</v>
+        <v>8459</v>
       </c>
       <c r="P4" t="s">
-        <v>7589</v>
+        <v>8463</v>
       </c>
       <c r="Q4" t="s">
-        <v>7610</v>
+        <v>8459</v>
       </c>
       <c r="R4" t="s">
-        <v>7632</v>
+        <v>8459</v>
       </c>
       <c r="S4" t="s">
-        <v>7655</v>
+        <v>8459</v>
       </c>
       <c r="T4" t="s">
-        <v>7676</v>
+        <v>8463</v>
       </c>
       <c r="U4" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V4" t="s">
-        <v>7688</v>
+        <v>8463</v>
       </c>
       <c r="W4" t="s">
-        <v>7708</v>
+        <v>8463</v>
       </c>
       <c r="X4" t="s">
-        <v>7728</v>
+        <v>8463</v>
       </c>
       <c r="Y4" t="s">
-        <v>7750</v>
+        <v>8459</v>
       </c>
       <c r="Z4" t="s">
-        <v>7772</v>
+        <v>8459</v>
       </c>
       <c r="AA4" t="s">
-        <v>7794</v>
+        <v>8463</v>
       </c>
       <c r="AB4" t="s">
-        <v>7817</v>
+        <v>8463</v>
       </c>
       <c r="AC4" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD4" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE4" t="s">
-        <v>7841</v>
+        <v>8459</v>
       </c>
       <c r="AF4" t="s">
-        <v>7864</v>
+        <v>8459</v>
       </c>
       <c r="AG4" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH4" t="s">
-        <v>7889</v>
+        <v>8459</v>
       </c>
       <c r="AI4" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ4" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7385</v>
+        <v>7917</v>
       </c>
       <c r="B5" s="1">
         <v>2013</v>
       </c>
       <c r="C5" t="s">
-        <v>7405</v>
+        <v>8459</v>
       </c>
       <c r="D5" t="s">
-        <v>7427</v>
+        <v>8463</v>
       </c>
       <c r="E5" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F5" t="s">
-        <v>7447</v>
+        <v>8459</v>
       </c>
       <c r="G5" t="s">
-        <v>7466</v>
+        <v>8459</v>
       </c>
       <c r="H5" t="s">
-        <v>7480</v>
+        <v>8463</v>
       </c>
       <c r="I5" t="s">
-        <v>7499</v>
+        <v>8459</v>
       </c>
       <c r="J5" t="s">
-        <v>7519</v>
+        <v>8459</v>
       </c>
       <c r="K5" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L5" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M5" t="s">
-        <v>7545</v>
+        <v>8459</v>
       </c>
       <c r="N5" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O5" t="s">
-        <v>7567</v>
+        <v>8459</v>
       </c>
       <c r="P5" t="s">
-        <v>7590</v>
+        <v>8459</v>
       </c>
       <c r="Q5" t="s">
-        <v>7611</v>
+        <v>8459</v>
       </c>
       <c r="R5" t="s">
-        <v>7633</v>
+        <v>8459</v>
       </c>
       <c r="S5" t="s">
-        <v>7656</v>
+        <v>8459</v>
       </c>
       <c r="T5" t="s">
-        <v>7676</v>
+        <v>8463</v>
       </c>
       <c r="U5" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V5" t="s">
-        <v>7689</v>
+        <v>8459</v>
       </c>
       <c r="W5" t="s">
-        <v>7709</v>
+        <v>8459</v>
       </c>
       <c r="X5" t="s">
-        <v>7729</v>
+        <v>8459</v>
       </c>
       <c r="Y5" t="s">
-        <v>7751</v>
+        <v>8459</v>
       </c>
       <c r="Z5" t="s">
-        <v>7773</v>
+        <v>8459</v>
       </c>
       <c r="AA5" t="s">
-        <v>7795</v>
+        <v>8459</v>
       </c>
       <c r="AB5" t="s">
-        <v>7818</v>
+        <v>8459</v>
       </c>
       <c r="AC5" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD5" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE5" t="s">
-        <v>7842</v>
+        <v>8459</v>
       </c>
       <c r="AF5" t="s">
-        <v>7865</v>
+        <v>8463</v>
       </c>
       <c r="AG5" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH5" t="s">
-        <v>7890</v>
+        <v>8459</v>
       </c>
       <c r="AI5" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ5" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7386</v>
+        <v>7918</v>
       </c>
       <c r="B6" s="1">
         <v>2010</v>
       </c>
       <c r="C6" t="s">
-        <v>7406</v>
+        <v>8459</v>
       </c>
       <c r="D6" t="s">
-        <v>7427</v>
+        <v>8463</v>
       </c>
       <c r="E6" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F6" t="s">
-        <v>7448</v>
+        <v>8463</v>
       </c>
       <c r="G6" t="s">
-        <v>7467</v>
+        <v>8463</v>
       </c>
       <c r="H6" t="s">
-        <v>7480</v>
+        <v>8463</v>
       </c>
       <c r="I6" t="s">
-        <v>7500</v>
+        <v>8463</v>
       </c>
       <c r="J6" t="s">
-        <v>7520</v>
+        <v>8459</v>
       </c>
       <c r="K6" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L6" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M6" t="s">
-        <v>7546</v>
+        <v>8463</v>
       </c>
       <c r="N6" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O6" t="s">
-        <v>7568</v>
+        <v>8459</v>
       </c>
       <c r="P6" t="s">
-        <v>7591</v>
+        <v>8463</v>
       </c>
       <c r="Q6" t="s">
-        <v>7612</v>
+        <v>8459</v>
       </c>
       <c r="R6" t="s">
-        <v>7634</v>
+        <v>8459</v>
       </c>
       <c r="S6" t="s">
-        <v>7657</v>
+        <v>8459</v>
       </c>
       <c r="T6" t="s">
-        <v>7676</v>
+        <v>8463</v>
       </c>
       <c r="U6" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V6" t="s">
-        <v>7690</v>
+        <v>8463</v>
       </c>
       <c r="W6" t="s">
-        <v>7710</v>
+        <v>8463</v>
       </c>
       <c r="X6" t="s">
-        <v>7730</v>
+        <v>8459</v>
       </c>
       <c r="Y6" t="s">
-        <v>7752</v>
+        <v>8463</v>
       </c>
       <c r="Z6" t="s">
-        <v>7774</v>
+        <v>8463</v>
       </c>
       <c r="AA6" t="s">
-        <v>7796</v>
+        <v>8459</v>
       </c>
       <c r="AB6" t="s">
-        <v>7819</v>
+        <v>8463</v>
       </c>
       <c r="AC6" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD6" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE6" t="s">
-        <v>7843</v>
+        <v>8459</v>
       </c>
       <c r="AF6" t="s">
-        <v>7866</v>
+        <v>8459</v>
       </c>
       <c r="AG6" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH6" t="s">
-        <v>7891</v>
+        <v>8459</v>
       </c>
       <c r="AI6" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ6" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7386</v>
+        <v>7918</v>
       </c>
       <c r="B7" s="1">
         <v>2014</v>
       </c>
       <c r="C7" t="s">
-        <v>7407</v>
+        <v>8459</v>
       </c>
       <c r="D7" t="s">
-        <v>7427</v>
+        <v>8463</v>
       </c>
       <c r="E7" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F7" t="s">
-        <v>7448</v>
+        <v>8463</v>
       </c>
       <c r="G7" t="s">
-        <v>7467</v>
+        <v>8463</v>
       </c>
       <c r="H7" t="s">
-        <v>7480</v>
+        <v>8463</v>
       </c>
       <c r="I7" t="s">
-        <v>7500</v>
+        <v>8463</v>
       </c>
       <c r="J7" t="s">
-        <v>7521</v>
+        <v>8459</v>
       </c>
       <c r="K7" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L7" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M7" t="s">
-        <v>7546</v>
+        <v>8463</v>
       </c>
       <c r="N7" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O7" t="s">
-        <v>7569</v>
+        <v>8459</v>
       </c>
       <c r="P7" t="s">
-        <v>7591</v>
+        <v>8463</v>
       </c>
       <c r="Q7" t="s">
-        <v>7613</v>
+        <v>8459</v>
       </c>
       <c r="R7" t="s">
-        <v>7635</v>
+        <v>8459</v>
       </c>
       <c r="S7" t="s">
-        <v>7658</v>
+        <v>8459</v>
       </c>
       <c r="T7" t="s">
-        <v>7676</v>
+        <v>8463</v>
       </c>
       <c r="U7" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V7" t="s">
-        <v>7690</v>
+        <v>8463</v>
       </c>
       <c r="W7" t="s">
-        <v>7710</v>
+        <v>8463</v>
       </c>
       <c r="X7" t="s">
-        <v>7731</v>
+        <v>8459</v>
       </c>
       <c r="Y7" t="s">
-        <v>7752</v>
+        <v>8463</v>
       </c>
       <c r="Z7" t="s">
-        <v>7774</v>
+        <v>8463</v>
       </c>
       <c r="AA7" t="s">
-        <v>7797</v>
+        <v>8459</v>
       </c>
       <c r="AB7" t="s">
-        <v>7819</v>
+        <v>8463</v>
       </c>
       <c r="AC7" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD7" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE7" t="s">
-        <v>7844</v>
+        <v>8459</v>
       </c>
       <c r="AF7" t="s">
-        <v>7867</v>
+        <v>8459</v>
       </c>
       <c r="AG7" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH7" t="s">
-        <v>7892</v>
+        <v>8459</v>
       </c>
       <c r="AI7" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ7" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7387</v>
+        <v>7919</v>
       </c>
       <c r="B8" s="1">
         <v>2010</v>
       </c>
       <c r="C8" t="s">
-        <v>7408</v>
+        <v>8459</v>
       </c>
       <c r="D8" t="s">
-        <v>7428</v>
+        <v>8459</v>
       </c>
       <c r="E8" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F8" t="s">
-        <v>7449</v>
+        <v>8459</v>
       </c>
       <c r="G8" t="s">
-        <v>7468</v>
+        <v>8459</v>
       </c>
       <c r="H8" t="s">
-        <v>7481</v>
+        <v>8459</v>
       </c>
       <c r="I8" t="s">
-        <v>7501</v>
+        <v>8459</v>
       </c>
       <c r="J8" t="s">
-        <v>7522</v>
+        <v>8459</v>
       </c>
       <c r="K8" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L8" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M8" t="s">
-        <v>7547</v>
+        <v>8459</v>
       </c>
       <c r="N8" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O8" t="s">
-        <v>7570</v>
+        <v>8459</v>
       </c>
       <c r="P8" t="s">
-        <v>7592</v>
+        <v>8459</v>
       </c>
       <c r="Q8" t="s">
-        <v>7614</v>
+        <v>8459</v>
       </c>
       <c r="R8" t="s">
-        <v>7636</v>
+        <v>8459</v>
       </c>
       <c r="S8" t="s">
-        <v>7659</v>
+        <v>8459</v>
       </c>
       <c r="T8" t="s">
-        <v>7677</v>
+        <v>8459</v>
       </c>
       <c r="U8" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V8" t="s">
-        <v>7691</v>
+        <v>8459</v>
       </c>
       <c r="W8" t="s">
-        <v>7711</v>
+        <v>8459</v>
       </c>
       <c r="X8" t="s">
-        <v>7732</v>
+        <v>8459</v>
       </c>
       <c r="Y8" t="s">
-        <v>7753</v>
+        <v>8459</v>
       </c>
       <c r="Z8" t="s">
-        <v>7775</v>
+        <v>8459</v>
       </c>
       <c r="AA8" t="s">
-        <v>7798</v>
+        <v>8459</v>
       </c>
       <c r="AB8" t="s">
-        <v>7820</v>
+        <v>8459</v>
       </c>
       <c r="AC8" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD8" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE8" t="s">
-        <v>7845</v>
+        <v>8463</v>
       </c>
       <c r="AF8" t="s">
-        <v>7868</v>
+        <v>8459</v>
       </c>
       <c r="AG8" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH8" t="s">
-        <v>7893</v>
+        <v>8459</v>
       </c>
       <c r="AI8" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ8" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7388</v>
+        <v>7920</v>
       </c>
       <c r="B9" s="1">
         <v>2013</v>
       </c>
       <c r="C9" t="s">
-        <v>7409</v>
+        <v>8459</v>
       </c>
       <c r="D9" t="s">
-        <v>7429</v>
+        <v>8463</v>
       </c>
       <c r="E9" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F9" t="s">
-        <v>7450</v>
+        <v>8459</v>
       </c>
       <c r="G9" t="s">
-        <v>7469</v>
+        <v>8459</v>
       </c>
       <c r="H9" t="s">
-        <v>7482</v>
+        <v>8459</v>
       </c>
       <c r="I9" t="s">
-        <v>7502</v>
+        <v>8463</v>
       </c>
       <c r="J9" t="s">
-        <v>7523</v>
+        <v>8459</v>
       </c>
       <c r="K9" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L9" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M9" t="s">
-        <v>7548</v>
+        <v>8463</v>
       </c>
       <c r="N9" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O9" t="s">
-        <v>7571</v>
+        <v>8459</v>
       </c>
       <c r="P9" t="s">
-        <v>7593</v>
+        <v>8463</v>
       </c>
       <c r="Q9" t="s">
-        <v>7615</v>
+        <v>8459</v>
       </c>
       <c r="R9" t="s">
-        <v>7637</v>
+        <v>8459</v>
       </c>
       <c r="S9" t="s">
-        <v>7660</v>
+        <v>8459</v>
       </c>
       <c r="T9" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U9" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V9" t="s">
-        <v>7692</v>
+        <v>8463</v>
       </c>
       <c r="W9" t="s">
-        <v>7712</v>
+        <v>8463</v>
       </c>
       <c r="X9" t="s">
-        <v>7733</v>
+        <v>8459</v>
       </c>
       <c r="Y9" t="s">
-        <v>7754</v>
+        <v>8463</v>
       </c>
       <c r="Z9" t="s">
-        <v>7776</v>
+        <v>8463</v>
       </c>
       <c r="AA9" t="s">
-        <v>7799</v>
+        <v>8459</v>
       </c>
       <c r="AB9" t="s">
-        <v>7821</v>
+        <v>8463</v>
       </c>
       <c r="AC9" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD9" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE9" t="s">
-        <v>7846</v>
+        <v>8459</v>
       </c>
       <c r="AF9" t="s">
-        <v>7869</v>
+        <v>8459</v>
       </c>
       <c r="AG9" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH9" t="s">
-        <v>7894</v>
+        <v>8459</v>
       </c>
       <c r="AI9" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ9" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7389</v>
+        <v>7921</v>
       </c>
       <c r="B10" s="1">
         <v>2011</v>
       </c>
       <c r="C10" t="s">
-        <v>7410</v>
+        <v>8459</v>
       </c>
       <c r="D10" t="s">
-        <v>7429</v>
+        <v>8463</v>
       </c>
       <c r="E10" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F10" t="s">
-        <v>7451</v>
+        <v>8459</v>
       </c>
       <c r="G10" t="s">
-        <v>7470</v>
+        <v>8463</v>
       </c>
       <c r="H10" t="s">
-        <v>7483</v>
+        <v>8459</v>
       </c>
       <c r="I10" t="s">
-        <v>7503</v>
+        <v>8459</v>
       </c>
       <c r="J10" t="s">
-        <v>7524</v>
+        <v>8459</v>
       </c>
       <c r="K10" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L10" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M10" t="s">
-        <v>7549</v>
+        <v>8459</v>
       </c>
       <c r="N10" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O10" t="s">
-        <v>7572</v>
+        <v>8459</v>
       </c>
       <c r="P10" t="s">
-        <v>7594</v>
+        <v>8459</v>
       </c>
       <c r="Q10" t="s">
-        <v>7616</v>
+        <v>8459</v>
       </c>
       <c r="R10" t="s">
-        <v>7638</v>
+        <v>8459</v>
       </c>
       <c r="S10" t="s">
-        <v>7661</v>
+        <v>8459</v>
       </c>
       <c r="T10" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U10" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V10" t="s">
-        <v>7693</v>
+        <v>8459</v>
       </c>
       <c r="W10" t="s">
-        <v>7713</v>
+        <v>8459</v>
       </c>
       <c r="X10" t="s">
-        <v>7734</v>
+        <v>8459</v>
       </c>
       <c r="Y10" t="s">
-        <v>7755</v>
+        <v>8459</v>
       </c>
       <c r="Z10" t="s">
-        <v>7777</v>
+        <v>8459</v>
       </c>
       <c r="AA10" t="s">
-        <v>7800</v>
+        <v>8459</v>
       </c>
       <c r="AB10" t="s">
-        <v>7822</v>
+        <v>8459</v>
       </c>
       <c r="AC10" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD10" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE10" t="s">
-        <v>7847</v>
+        <v>8459</v>
       </c>
       <c r="AF10" t="s">
-        <v>7870</v>
+        <v>8459</v>
       </c>
       <c r="AG10" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH10" t="s">
-        <v>7895</v>
+        <v>8459</v>
       </c>
       <c r="AI10" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ10" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>7390</v>
+        <v>7922</v>
       </c>
       <c r="B11" s="1">
         <v>2011</v>
       </c>
       <c r="C11" t="s">
-        <v>7411</v>
+        <v>8459</v>
       </c>
       <c r="D11" t="s">
-        <v>7430</v>
+        <v>8459</v>
       </c>
       <c r="E11" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F11" t="s">
-        <v>7452</v>
+        <v>8459</v>
       </c>
       <c r="G11" t="s">
-        <v>7471</v>
+        <v>8459</v>
       </c>
       <c r="H11" t="s">
-        <v>7484</v>
+        <v>8459</v>
       </c>
       <c r="I11" t="s">
-        <v>7504</v>
+        <v>8459</v>
       </c>
       <c r="J11" t="s">
-        <v>7525</v>
+        <v>8463</v>
       </c>
       <c r="K11" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L11" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M11" t="s">
-        <v>7550</v>
+        <v>8463</v>
       </c>
       <c r="N11" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O11" t="s">
-        <v>7573</v>
+        <v>8459</v>
       </c>
       <c r="P11" t="s">
-        <v>7595</v>
+        <v>8463</v>
       </c>
       <c r="Q11" t="s">
-        <v>7617</v>
+        <v>8459</v>
       </c>
       <c r="R11" t="s">
-        <v>7639</v>
+        <v>8459</v>
       </c>
       <c r="S11" t="s">
-        <v>7662</v>
+        <v>8459</v>
       </c>
       <c r="T11" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U11" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V11" t="s">
-        <v>7694</v>
+        <v>8463</v>
       </c>
       <c r="W11" t="s">
-        <v>7714</v>
+        <v>8463</v>
       </c>
       <c r="X11" t="s">
-        <v>7735</v>
+        <v>8459</v>
       </c>
       <c r="Y11" t="s">
-        <v>7756</v>
+        <v>8459</v>
       </c>
       <c r="Z11" t="s">
-        <v>7778</v>
+        <v>8463</v>
       </c>
       <c r="AA11" t="s">
-        <v>7801</v>
+        <v>8459</v>
       </c>
       <c r="AB11" t="s">
-        <v>7823</v>
+        <v>8463</v>
       </c>
       <c r="AC11" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD11" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE11" t="s">
-        <v>7848</v>
+        <v>8459</v>
       </c>
       <c r="AF11" t="s">
-        <v>7871</v>
+        <v>8459</v>
       </c>
       <c r="AG11" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH11" t="s">
-        <v>7896</v>
+        <v>8459</v>
       </c>
       <c r="AI11" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ11" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>7391</v>
+        <v>7923</v>
       </c>
       <c r="B12" s="1">
         <v>2011</v>
       </c>
       <c r="C12" t="s">
-        <v>7412</v>
+        <v>8459</v>
       </c>
       <c r="D12" t="s">
-        <v>7431</v>
+        <v>8459</v>
       </c>
       <c r="E12" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F12" t="s">
-        <v>7453</v>
+        <v>8459</v>
       </c>
       <c r="G12" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H12" t="s">
-        <v>7485</v>
+        <v>8459</v>
       </c>
       <c r="I12" t="s">
-        <v>7505</v>
+        <v>8459</v>
       </c>
       <c r="J12" t="s">
-        <v>7526</v>
+        <v>8459</v>
       </c>
       <c r="K12" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L12" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M12" t="s">
-        <v>7551</v>
+        <v>8459</v>
       </c>
       <c r="N12" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O12" t="s">
-        <v>7574</v>
+        <v>8459</v>
       </c>
       <c r="P12" t="s">
-        <v>7596</v>
+        <v>8459</v>
       </c>
       <c r="Q12" t="s">
-        <v>7618</v>
+        <v>8459</v>
       </c>
       <c r="R12" t="s">
-        <v>7640</v>
+        <v>8459</v>
       </c>
       <c r="S12" t="s">
-        <v>7663</v>
+        <v>8459</v>
       </c>
       <c r="T12" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U12" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V12" t="s">
-        <v>7695</v>
+        <v>8459</v>
       </c>
       <c r="W12" t="s">
-        <v>7715</v>
+        <v>8459</v>
       </c>
       <c r="X12" t="s">
-        <v>7736</v>
+        <v>8459</v>
       </c>
       <c r="Y12" t="s">
-        <v>7757</v>
+        <v>8459</v>
       </c>
       <c r="Z12" t="s">
-        <v>7779</v>
+        <v>8459</v>
       </c>
       <c r="AA12" t="s">
-        <v>7802</v>
+        <v>8459</v>
       </c>
       <c r="AB12" t="s">
-        <v>7824</v>
+        <v>8459</v>
       </c>
       <c r="AC12" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD12" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE12" t="s">
-        <v>7849</v>
+        <v>8459</v>
       </c>
       <c r="AF12" t="s">
-        <v>7872</v>
+        <v>8459</v>
       </c>
       <c r="AG12" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH12" t="s">
-        <v>7897</v>
+        <v>8459</v>
       </c>
       <c r="AI12" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ12" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7392</v>
+        <v>7924</v>
       </c>
       <c r="B13" s="1">
         <v>2011</v>
       </c>
       <c r="C13" t="s">
-        <v>7413</v>
+        <v>8459</v>
       </c>
       <c r="D13" t="s">
-        <v>7432</v>
+        <v>8459</v>
       </c>
       <c r="E13" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F13" t="s">
-        <v>7454</v>
+        <v>8459</v>
       </c>
       <c r="G13" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H13" t="s">
-        <v>7486</v>
+        <v>8459</v>
       </c>
       <c r="I13" t="s">
-        <v>7506</v>
+        <v>8459</v>
       </c>
       <c r="J13" t="s">
-        <v>7527</v>
+        <v>8459</v>
       </c>
       <c r="K13" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L13" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M13" t="s">
-        <v>7552</v>
+        <v>8459</v>
       </c>
       <c r="N13" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O13" t="s">
-        <v>7575</v>
+        <v>8459</v>
       </c>
       <c r="P13" t="s">
-        <v>7597</v>
+        <v>8459</v>
       </c>
       <c r="Q13" t="s">
-        <v>7619</v>
+        <v>8459</v>
       </c>
       <c r="R13" t="s">
-        <v>7641</v>
+        <v>8459</v>
       </c>
       <c r="S13" t="s">
-        <v>7664</v>
+        <v>8459</v>
       </c>
       <c r="T13" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U13" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V13" t="s">
-        <v>7696</v>
+        <v>8459</v>
       </c>
       <c r="W13" t="s">
-        <v>7716</v>
+        <v>8459</v>
       </c>
       <c r="X13" t="s">
-        <v>7737</v>
+        <v>8459</v>
       </c>
       <c r="Y13" t="s">
-        <v>7758</v>
+        <v>8459</v>
       </c>
       <c r="Z13" t="s">
-        <v>7780</v>
+        <v>8459</v>
       </c>
       <c r="AA13" t="s">
-        <v>7803</v>
+        <v>8459</v>
       </c>
       <c r="AB13" t="s">
-        <v>7825</v>
+        <v>8459</v>
       </c>
       <c r="AC13" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD13" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE13" t="s">
-        <v>7850</v>
+        <v>8459</v>
       </c>
       <c r="AF13" t="s">
-        <v>7873</v>
+        <v>8459</v>
       </c>
       <c r="AG13" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH13" t="s">
-        <v>7898</v>
+        <v>8459</v>
       </c>
       <c r="AI13" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ13" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>7393</v>
+        <v>7925</v>
       </c>
       <c r="B14" s="1">
         <v>2010</v>
       </c>
       <c r="C14" t="s">
-        <v>7414</v>
+        <v>8459</v>
       </c>
       <c r="D14" t="s">
-        <v>7433</v>
+        <v>8463</v>
       </c>
       <c r="E14" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F14" t="s">
-        <v>7455</v>
+        <v>8459</v>
       </c>
       <c r="G14" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H14" t="s">
-        <v>7487</v>
+        <v>8459</v>
       </c>
       <c r="I14" t="s">
-        <v>7507</v>
+        <v>8459</v>
       </c>
       <c r="J14" t="s">
-        <v>7528</v>
+        <v>8459</v>
       </c>
       <c r="K14" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L14" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M14" t="s">
-        <v>7553</v>
+        <v>8459</v>
       </c>
       <c r="N14" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O14" t="s">
-        <v>7576</v>
+        <v>8459</v>
       </c>
       <c r="P14" t="s">
-        <v>7598</v>
+        <v>8459</v>
       </c>
       <c r="Q14" t="s">
-        <v>7620</v>
+        <v>8459</v>
       </c>
       <c r="R14" t="s">
-        <v>7642</v>
+        <v>8459</v>
       </c>
       <c r="S14" t="s">
-        <v>7665</v>
+        <v>8459</v>
       </c>
       <c r="T14" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U14" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V14" t="s">
-        <v>7697</v>
+        <v>8459</v>
       </c>
       <c r="W14" t="s">
-        <v>7717</v>
+        <v>8459</v>
       </c>
       <c r="X14" t="s">
-        <v>7738</v>
+        <v>8459</v>
       </c>
       <c r="Y14" t="s">
-        <v>7759</v>
+        <v>8459</v>
       </c>
       <c r="Z14" t="s">
-        <v>7781</v>
+        <v>8459</v>
       </c>
       <c r="AA14" t="s">
-        <v>7804</v>
+        <v>8459</v>
       </c>
       <c r="AB14" t="s">
-        <v>7826</v>
+        <v>8459</v>
       </c>
       <c r="AC14" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD14" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE14" t="s">
-        <v>7851</v>
+        <v>8463</v>
       </c>
       <c r="AF14" t="s">
-        <v>7874</v>
+        <v>8459</v>
       </c>
       <c r="AG14" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH14" t="s">
-        <v>7899</v>
+        <v>8459</v>
       </c>
       <c r="AI14" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ14" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>7393</v>
+        <v>7925</v>
       </c>
       <c r="B15" s="1">
         <v>2012</v>
       </c>
       <c r="C15" t="s">
-        <v>7415</v>
+        <v>8459</v>
       </c>
       <c r="D15" t="s">
-        <v>7433</v>
+        <v>8463</v>
       </c>
       <c r="E15" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F15" t="s">
-        <v>7456</v>
+        <v>8463</v>
       </c>
       <c r="G15" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H15" t="s">
-        <v>7488</v>
+        <v>8463</v>
       </c>
       <c r="I15" t="s">
-        <v>7508</v>
+        <v>8463</v>
       </c>
       <c r="J15" t="s">
-        <v>7529</v>
+        <v>8463</v>
       </c>
       <c r="K15" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L15" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M15" t="s">
-        <v>7554</v>
+        <v>8463</v>
       </c>
       <c r="N15" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O15" t="s">
-        <v>7577</v>
+        <v>8463</v>
       </c>
       <c r="P15" t="s">
-        <v>7599</v>
+        <v>8463</v>
       </c>
       <c r="Q15" t="s">
-        <v>7621</v>
+        <v>8463</v>
       </c>
       <c r="R15" t="s">
-        <v>7643</v>
+        <v>8459</v>
       </c>
       <c r="S15" t="s">
-        <v>7666</v>
+        <v>8459</v>
       </c>
       <c r="T15" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U15" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V15" t="s">
-        <v>7698</v>
+        <v>8463</v>
       </c>
       <c r="W15" t="s">
-        <v>7718</v>
+        <v>8463</v>
       </c>
       <c r="X15" t="s">
-        <v>7739</v>
+        <v>8463</v>
       </c>
       <c r="Y15" t="s">
-        <v>7760</v>
+        <v>8459</v>
       </c>
       <c r="Z15" t="s">
-        <v>7782</v>
+        <v>8459</v>
       </c>
       <c r="AA15" t="s">
-        <v>7805</v>
+        <v>8459</v>
       </c>
       <c r="AB15" t="s">
-        <v>7827</v>
+        <v>8463</v>
       </c>
       <c r="AC15" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD15" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE15" t="s">
-        <v>7852</v>
+        <v>8459</v>
       </c>
       <c r="AF15" t="s">
-        <v>7875</v>
+        <v>8459</v>
       </c>
       <c r="AG15" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH15" t="s">
-        <v>7900</v>
+        <v>8459</v>
       </c>
       <c r="AI15" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ15" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>7393</v>
+        <v>7925</v>
       </c>
       <c r="B16" s="1">
         <v>2014</v>
       </c>
       <c r="C16" t="s">
-        <v>7416</v>
+        <v>8459</v>
       </c>
       <c r="D16" t="s">
-        <v>7433</v>
+        <v>8463</v>
       </c>
       <c r="E16" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F16" t="s">
-        <v>7456</v>
+        <v>8463</v>
       </c>
       <c r="G16" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H16" t="s">
-        <v>7488</v>
+        <v>8463</v>
       </c>
       <c r="I16" t="s">
-        <v>7508</v>
+        <v>8463</v>
       </c>
       <c r="J16" t="s">
-        <v>7529</v>
+        <v>8463</v>
       </c>
       <c r="K16" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L16" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M16" t="s">
-        <v>7554</v>
+        <v>8463</v>
       </c>
       <c r="N16" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O16" t="s">
-        <v>7578</v>
+        <v>8459</v>
       </c>
       <c r="P16" t="s">
-        <v>7599</v>
+        <v>8463</v>
       </c>
       <c r="Q16" t="s">
-        <v>7621</v>
+        <v>8463</v>
       </c>
       <c r="R16" t="s">
-        <v>7644</v>
+        <v>8459</v>
       </c>
       <c r="S16" t="s">
-        <v>7667</v>
+        <v>8459</v>
       </c>
       <c r="T16" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U16" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V16" t="s">
-        <v>7698</v>
+        <v>8463</v>
       </c>
       <c r="W16" t="s">
-        <v>7718</v>
+        <v>8463</v>
       </c>
       <c r="X16" t="s">
-        <v>7739</v>
+        <v>8463</v>
       </c>
       <c r="Y16" t="s">
-        <v>7761</v>
+        <v>8459</v>
       </c>
       <c r="Z16" t="s">
-        <v>7783</v>
+        <v>8459</v>
       </c>
       <c r="AA16" t="s">
-        <v>7806</v>
+        <v>8459</v>
       </c>
       <c r="AB16" t="s">
-        <v>7827</v>
+        <v>8463</v>
       </c>
       <c r="AC16" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD16" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE16" t="s">
-        <v>7853</v>
+        <v>8459</v>
       </c>
       <c r="AF16" t="s">
-        <v>7876</v>
+        <v>8459</v>
       </c>
       <c r="AG16" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH16" t="s">
-        <v>7901</v>
+        <v>8459</v>
       </c>
       <c r="AI16" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ16" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>7394</v>
+        <v>7926</v>
       </c>
       <c r="B17" s="1">
         <v>2009</v>
       </c>
       <c r="C17" t="s">
-        <v>7417</v>
+        <v>8459</v>
       </c>
       <c r="D17" t="s">
-        <v>7434</v>
+        <v>8459</v>
       </c>
       <c r="E17" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F17" t="s">
-        <v>7457</v>
+        <v>8459</v>
       </c>
       <c r="G17" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H17" t="s">
-        <v>7489</v>
+        <v>8459</v>
       </c>
       <c r="I17" t="s">
-        <v>7509</v>
+        <v>8459</v>
       </c>
       <c r="J17" t="s">
-        <v>7530</v>
+        <v>8459</v>
       </c>
       <c r="K17" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L17" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M17" t="s">
-        <v>7555</v>
+        <v>8459</v>
       </c>
       <c r="N17" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O17" t="s">
-        <v>7579</v>
+        <v>8459</v>
       </c>
       <c r="P17" t="s">
-        <v>7600</v>
+        <v>8459</v>
       </c>
       <c r="Q17" t="s">
-        <v>7622</v>
+        <v>8459</v>
       </c>
       <c r="R17" t="s">
-        <v>7645</v>
+        <v>8459</v>
       </c>
       <c r="S17" t="s">
-        <v>7668</v>
+        <v>8459</v>
       </c>
       <c r="T17" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U17" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V17" t="s">
-        <v>7699</v>
+        <v>8459</v>
       </c>
       <c r="W17" t="s">
-        <v>7719</v>
+        <v>8459</v>
       </c>
       <c r="X17" t="s">
-        <v>7740</v>
+        <v>8459</v>
       </c>
       <c r="Y17" t="s">
-        <v>7762</v>
+        <v>8459</v>
       </c>
       <c r="Z17" t="s">
-        <v>7784</v>
+        <v>8459</v>
       </c>
       <c r="AA17" t="s">
-        <v>7807</v>
+        <v>8459</v>
       </c>
       <c r="AB17" t="s">
-        <v>7828</v>
+        <v>8459</v>
       </c>
       <c r="AC17" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD17" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE17" t="s">
-        <v>7854</v>
+        <v>8459</v>
       </c>
       <c r="AF17" t="s">
-        <v>7877</v>
+        <v>8459</v>
       </c>
       <c r="AG17" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH17" t="s">
-        <v>7902</v>
+        <v>8459</v>
       </c>
       <c r="AI17" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ17" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>7395</v>
+        <v>7927</v>
       </c>
       <c r="B18" s="1">
         <v>2016</v>
       </c>
       <c r="C18" t="s">
-        <v>7418</v>
+        <v>8459</v>
       </c>
       <c r="D18" t="s">
-        <v>7435</v>
+        <v>8463</v>
       </c>
       <c r="E18" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F18" t="s">
-        <v>7458</v>
+        <v>8463</v>
       </c>
       <c r="G18" t="s">
-        <v>7472</v>
+        <v>8463</v>
       </c>
       <c r="H18" t="s">
-        <v>7490</v>
+        <v>8463</v>
       </c>
       <c r="I18" t="s">
-        <v>7510</v>
+        <v>8463</v>
       </c>
       <c r="J18" t="s">
-        <v>7531</v>
+        <v>8463</v>
       </c>
       <c r="K18" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L18" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M18" t="s">
-        <v>7556</v>
+        <v>8463</v>
       </c>
       <c r="N18" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O18" t="s">
-        <v>7580</v>
+        <v>8463</v>
       </c>
       <c r="P18" t="s">
-        <v>7601</v>
+        <v>8463</v>
       </c>
       <c r="Q18" t="s">
-        <v>7623</v>
+        <v>8459</v>
       </c>
       <c r="R18" t="s">
-        <v>7646</v>
+        <v>8459</v>
       </c>
       <c r="S18" t="s">
-        <v>7669</v>
+        <v>8463</v>
       </c>
       <c r="T18" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U18" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V18" t="s">
-        <v>7700</v>
+        <v>8463</v>
       </c>
       <c r="W18" t="s">
-        <v>7720</v>
+        <v>8463</v>
       </c>
       <c r="X18" t="s">
-        <v>7741</v>
+        <v>8463</v>
       </c>
       <c r="Y18" t="s">
-        <v>7763</v>
+        <v>8459</v>
       </c>
       <c r="Z18" t="s">
-        <v>7785</v>
+        <v>8459</v>
       </c>
       <c r="AA18" t="s">
-        <v>7808</v>
+        <v>8459</v>
       </c>
       <c r="AB18" t="s">
-        <v>7829</v>
+        <v>8463</v>
       </c>
       <c r="AC18" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD18" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE18" t="s">
-        <v>7855</v>
+        <v>8459</v>
       </c>
       <c r="AF18" t="s">
-        <v>7878</v>
+        <v>8459</v>
       </c>
       <c r="AG18" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH18" t="s">
-        <v>7903</v>
+        <v>8459</v>
       </c>
       <c r="AI18" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ18" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>7396</v>
+        <v>7928</v>
       </c>
       <c r="B19" s="1">
         <v>2014</v>
       </c>
       <c r="C19" t="s">
-        <v>7419</v>
+        <v>8459</v>
       </c>
       <c r="D19" t="s">
-        <v>7435</v>
+        <v>8463</v>
       </c>
       <c r="E19" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F19" t="s">
-        <v>7459</v>
+        <v>8459</v>
       </c>
       <c r="G19" t="s">
-        <v>7473</v>
+        <v>8459</v>
       </c>
       <c r="H19" t="s">
-        <v>7491</v>
+        <v>8459</v>
       </c>
       <c r="I19" t="s">
-        <v>7511</v>
+        <v>8459</v>
       </c>
       <c r="J19" t="s">
-        <v>7532</v>
+        <v>8459</v>
       </c>
       <c r="K19" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L19" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M19" t="s">
-        <v>7557</v>
+        <v>8459</v>
       </c>
       <c r="N19" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O19" t="s">
-        <v>7581</v>
+        <v>8459</v>
       </c>
       <c r="P19" t="s">
-        <v>7602</v>
+        <v>8459</v>
       </c>
       <c r="Q19" t="s">
-        <v>7624</v>
+        <v>8459</v>
       </c>
       <c r="R19" t="s">
-        <v>7647</v>
+        <v>8459</v>
       </c>
       <c r="S19" t="s">
-        <v>7670</v>
+        <v>8459</v>
       </c>
       <c r="T19" t="s">
-        <v>7678</v>
+        <v>8463</v>
       </c>
       <c r="U19" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V19" t="s">
-        <v>7701</v>
+        <v>8459</v>
       </c>
       <c r="W19" t="s">
-        <v>7721</v>
+        <v>8459</v>
       </c>
       <c r="X19" t="s">
-        <v>7742</v>
+        <v>8459</v>
       </c>
       <c r="Y19" t="s">
-        <v>7764</v>
+        <v>8459</v>
       </c>
       <c r="Z19" t="s">
-        <v>7786</v>
+        <v>8459</v>
       </c>
       <c r="AA19" t="s">
-        <v>7809</v>
+        <v>8459</v>
       </c>
       <c r="AB19" t="s">
-        <v>7830</v>
+        <v>8459</v>
       </c>
       <c r="AC19" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD19" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE19" t="s">
-        <v>7856</v>
+        <v>8459</v>
       </c>
       <c r="AF19" t="s">
-        <v>7879</v>
+        <v>8463</v>
       </c>
       <c r="AG19" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH19" t="s">
-        <v>7904</v>
+        <v>8459</v>
       </c>
       <c r="AI19" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ19" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>7397</v>
+        <v>7929</v>
       </c>
       <c r="B20" s="1">
         <v>2009</v>
       </c>
       <c r="C20" t="s">
-        <v>7420</v>
+        <v>8459</v>
       </c>
       <c r="D20" t="s">
-        <v>7436</v>
+        <v>8459</v>
       </c>
       <c r="E20" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F20" t="s">
-        <v>7460</v>
+        <v>8459</v>
       </c>
       <c r="G20" t="s">
-        <v>7474</v>
+        <v>8459</v>
       </c>
       <c r="H20" t="s">
-        <v>7492</v>
+        <v>8459</v>
       </c>
       <c r="I20" t="s">
-        <v>7512</v>
+        <v>8459</v>
       </c>
       <c r="J20" t="s">
-        <v>7533</v>
+        <v>8459</v>
       </c>
       <c r="K20" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L20" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M20" t="s">
-        <v>7558</v>
+        <v>8459</v>
       </c>
       <c r="N20" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O20" t="s">
-        <v>7582</v>
+        <v>8459</v>
       </c>
       <c r="P20" t="s">
-        <v>7603</v>
+        <v>8459</v>
       </c>
       <c r="Q20" t="s">
-        <v>7625</v>
+        <v>8459</v>
       </c>
       <c r="R20" t="s">
-        <v>7648</v>
+        <v>8459</v>
       </c>
       <c r="S20" t="s">
-        <v>7671</v>
+        <v>8459</v>
       </c>
       <c r="T20" t="s">
-        <v>7679</v>
+        <v>8459</v>
       </c>
       <c r="U20" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V20" t="s">
-        <v>7702</v>
+        <v>8459</v>
       </c>
       <c r="W20" t="s">
-        <v>7722</v>
+        <v>8459</v>
       </c>
       <c r="X20" t="s">
-        <v>7743</v>
+        <v>8459</v>
       </c>
       <c r="Y20" t="s">
-        <v>7765</v>
+        <v>8459</v>
       </c>
       <c r="Z20" t="s">
-        <v>7787</v>
+        <v>8459</v>
       </c>
       <c r="AA20" t="s">
-        <v>7810</v>
+        <v>8459</v>
       </c>
       <c r="AB20" t="s">
-        <v>7831</v>
+        <v>8459</v>
       </c>
       <c r="AC20" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD20" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE20" t="s">
-        <v>7857</v>
+        <v>8459</v>
       </c>
       <c r="AF20" t="s">
-        <v>7880</v>
+        <v>8459</v>
       </c>
       <c r="AG20" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH20" t="s">
-        <v>7905</v>
+        <v>8459</v>
       </c>
       <c r="AI20" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ20" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>7397</v>
+        <v>7929</v>
       </c>
       <c r="B21" s="1">
         <v>2011</v>
       </c>
       <c r="C21" t="s">
-        <v>7421</v>
+        <v>8459</v>
       </c>
       <c r="D21" t="s">
-        <v>7437</v>
+        <v>8463</v>
       </c>
       <c r="E21" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F21" t="s">
-        <v>7461</v>
+        <v>8463</v>
       </c>
       <c r="G21" t="s">
-        <v>7475</v>
+        <v>8463</v>
       </c>
       <c r="H21" t="s">
-        <v>7493</v>
+        <v>8463</v>
       </c>
       <c r="I21" t="s">
-        <v>7513</v>
+        <v>8463</v>
       </c>
       <c r="J21" t="s">
-        <v>7534</v>
+        <v>8459</v>
       </c>
       <c r="K21" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L21" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M21" t="s">
-        <v>7559</v>
+        <v>8463</v>
       </c>
       <c r="N21" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O21" t="s">
-        <v>7583</v>
+        <v>8459</v>
       </c>
       <c r="P21" t="s">
-        <v>7604</v>
+        <v>8459</v>
       </c>
       <c r="Q21" t="s">
-        <v>7626</v>
+        <v>8459</v>
       </c>
       <c r="R21" t="s">
-        <v>7649</v>
+        <v>8459</v>
       </c>
       <c r="S21" t="s">
-        <v>7672</v>
+        <v>8459</v>
       </c>
       <c r="T21" t="s">
-        <v>7680</v>
+        <v>8459</v>
       </c>
       <c r="U21" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V21" t="s">
-        <v>7703</v>
+        <v>8463</v>
       </c>
       <c r="W21" t="s">
-        <v>7723</v>
+        <v>8463</v>
       </c>
       <c r="X21" t="s">
-        <v>7744</v>
+        <v>8463</v>
       </c>
       <c r="Y21" t="s">
-        <v>7766</v>
+        <v>8459</v>
       </c>
       <c r="Z21" t="s">
-        <v>7788</v>
+        <v>8459</v>
       </c>
       <c r="AA21" t="s">
-        <v>7811</v>
+        <v>8459</v>
       </c>
       <c r="AB21" t="s">
-        <v>7832</v>
+        <v>8463</v>
       </c>
       <c r="AC21" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD21" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE21" t="s">
-        <v>7858</v>
+        <v>8459</v>
       </c>
       <c r="AF21" t="s">
-        <v>7881</v>
+        <v>8459</v>
       </c>
       <c r="AG21" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH21" t="s">
-        <v>7906</v>
+        <v>8459</v>
       </c>
       <c r="AI21" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ21" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>7398</v>
+        <v>7930</v>
       </c>
       <c r="B22" s="1">
         <v>2009</v>
       </c>
       <c r="C22" t="s">
-        <v>7422</v>
+        <v>8459</v>
       </c>
       <c r="D22" t="s">
-        <v>7437</v>
+        <v>8463</v>
       </c>
       <c r="E22" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F22" t="s">
-        <v>7461</v>
+        <v>8463</v>
       </c>
       <c r="G22" t="s">
-        <v>7475</v>
+        <v>8463</v>
       </c>
       <c r="H22" t="s">
-        <v>7493</v>
+        <v>8463</v>
       </c>
       <c r="I22" t="s">
-        <v>7513</v>
+        <v>8463</v>
       </c>
       <c r="J22" t="s">
-        <v>7535</v>
+        <v>8463</v>
       </c>
       <c r="K22" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L22" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M22" t="s">
-        <v>7559</v>
+        <v>8463</v>
       </c>
       <c r="N22" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O22" t="s">
-        <v>7584</v>
+        <v>8459</v>
       </c>
       <c r="P22" t="s">
-        <v>7605</v>
+        <v>8459</v>
       </c>
       <c r="Q22" t="s">
-        <v>7627</v>
+        <v>8459</v>
       </c>
       <c r="R22" t="s">
-        <v>7650</v>
+        <v>8459</v>
       </c>
       <c r="S22" t="s">
-        <v>7673</v>
+        <v>8459</v>
       </c>
       <c r="T22" t="s">
-        <v>7681</v>
+        <v>8459</v>
       </c>
       <c r="U22" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V22" t="s">
-        <v>7703</v>
+        <v>8463</v>
       </c>
       <c r="W22" t="s">
-        <v>7723</v>
+        <v>8463</v>
       </c>
       <c r="X22" t="s">
-        <v>7745</v>
+        <v>8459</v>
       </c>
       <c r="Y22" t="s">
-        <v>7767</v>
+        <v>8463</v>
       </c>
       <c r="Z22" t="s">
-        <v>7789</v>
+        <v>8463</v>
       </c>
       <c r="AA22" t="s">
-        <v>7812</v>
+        <v>8459</v>
       </c>
       <c r="AB22" t="s">
-        <v>7832</v>
+        <v>8463</v>
       </c>
       <c r="AC22" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD22" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE22" t="s">
-        <v>7859</v>
+        <v>8459</v>
       </c>
       <c r="AF22" t="s">
-        <v>7882</v>
+        <v>8459</v>
       </c>
       <c r="AG22" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH22" t="s">
-        <v>7907</v>
+        <v>8459</v>
       </c>
       <c r="AI22" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ22" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>7399</v>
+        <v>7931</v>
       </c>
       <c r="B23" s="1">
         <v>2013</v>
       </c>
       <c r="C23" t="s">
-        <v>7423</v>
+        <v>8459</v>
       </c>
       <c r="D23" t="s">
-        <v>7438</v>
+        <v>8459</v>
       </c>
       <c r="E23" t="s">
-        <v>7442</v>
+        <v>8463</v>
       </c>
       <c r="F23" t="s">
-        <v>7461</v>
+        <v>8463</v>
       </c>
       <c r="G23" t="s">
-        <v>7476</v>
+        <v>8459</v>
       </c>
       <c r="H23" t="s">
-        <v>7494</v>
+        <v>8459</v>
       </c>
       <c r="I23" t="s">
-        <v>7514</v>
+        <v>8459</v>
       </c>
       <c r="J23" t="s">
-        <v>7536</v>
+        <v>8459</v>
       </c>
       <c r="K23" t="s">
-        <v>7538</v>
+        <v>8463</v>
       </c>
       <c r="L23" t="s">
-        <v>7540</v>
+        <v>8463</v>
       </c>
       <c r="M23" t="s">
-        <v>7560</v>
+        <v>8459</v>
       </c>
       <c r="N23" t="s">
-        <v>7562</v>
+        <v>8463</v>
       </c>
       <c r="O23" t="s">
-        <v>7585</v>
+        <v>8459</v>
       </c>
       <c r="P23" t="s">
-        <v>7606</v>
+        <v>8459</v>
       </c>
       <c r="Q23" t="s">
-        <v>7628</v>
+        <v>8459</v>
       </c>
       <c r="R23" t="s">
-        <v>7651</v>
+        <v>8459</v>
       </c>
       <c r="S23" t="s">
-        <v>7674</v>
+        <v>8459</v>
       </c>
       <c r="T23" t="s">
-        <v>7682</v>
+        <v>8463</v>
       </c>
       <c r="U23" t="s">
-        <v>7684</v>
+        <v>8463</v>
       </c>
       <c r="V23" t="s">
-        <v>7704</v>
+        <v>8459</v>
       </c>
       <c r="W23" t="s">
-        <v>7724</v>
+        <v>8459</v>
       </c>
       <c r="X23" t="s">
-        <v>7746</v>
+        <v>8459</v>
       </c>
       <c r="Y23" t="s">
-        <v>7768</v>
+        <v>8459</v>
       </c>
       <c r="Z23" t="s">
-        <v>7790</v>
+        <v>8459</v>
       </c>
       <c r="AA23" t="s">
-        <v>7813</v>
+        <v>8459</v>
       </c>
       <c r="AB23" t="s">
-        <v>7833</v>
+        <v>8459</v>
       </c>
       <c r="AC23" t="s">
-        <v>7835</v>
+        <v>8463</v>
       </c>
       <c r="AD23" t="s">
-        <v>7837</v>
+        <v>8463</v>
       </c>
       <c r="AE23" t="s">
-        <v>7860</v>
+        <v>8459</v>
       </c>
       <c r="AF23" t="s">
-        <v>7883</v>
+        <v>8459</v>
       </c>
       <c r="AG23" t="s">
-        <v>7885</v>
+        <v>8463</v>
       </c>
       <c r="AH23" t="s">
-        <v>7908</v>
+        <v>8459</v>
       </c>
       <c r="AI23" t="s">
-        <v>7910</v>
+        <v>8463</v>
       </c>
       <c r="AJ23" t="s">
-        <v>7912</v>
+        <v>8463</v>
       </c>
     </row>
   </sheetData>
@@ -28108,100 +28108,100 @@
         <v>2012</v>
       </c>
       <c r="C2" t="s">
-        <v>7934</v>
+        <v>8459</v>
       </c>
       <c r="D2" t="s">
-        <v>7951</v>
+        <v>8459</v>
       </c>
       <c r="E2" t="s">
-        <v>7971</v>
+        <v>8463</v>
       </c>
       <c r="F2" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G2" t="s">
-        <v>7992</v>
+        <v>8459</v>
       </c>
       <c r="H2" t="s">
-        <v>8012</v>
+        <v>8459</v>
       </c>
       <c r="I2" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J2" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K2" t="s">
-        <v>8046</v>
+        <v>8459</v>
       </c>
       <c r="L2" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M2" t="s">
-        <v>8072</v>
+        <v>8459</v>
       </c>
       <c r="N2" t="s">
-        <v>8095</v>
+        <v>8459</v>
       </c>
       <c r="O2" t="s">
-        <v>8116</v>
+        <v>8459</v>
       </c>
       <c r="P2" t="s">
-        <v>8138</v>
+        <v>8459</v>
       </c>
       <c r="Q2" t="s">
-        <v>8161</v>
+        <v>8459</v>
       </c>
       <c r="R2" t="s">
-        <v>8184</v>
+        <v>8463</v>
       </c>
       <c r="S2" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T2" t="s">
-        <v>8201</v>
+        <v>8459</v>
       </c>
       <c r="U2" t="s">
-        <v>8221</v>
+        <v>8459</v>
       </c>
       <c r="V2" t="s">
-        <v>8241</v>
+        <v>8459</v>
       </c>
       <c r="W2" t="s">
-        <v>8263</v>
+        <v>8459</v>
       </c>
       <c r="X2" t="s">
-        <v>8285</v>
+        <v>8459</v>
       </c>
       <c r="Y2" t="s">
-        <v>8307</v>
+        <v>8459</v>
       </c>
       <c r="Z2" t="s">
-        <v>8330</v>
+        <v>8459</v>
       </c>
       <c r="AA2" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB2" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC2" t="s">
-        <v>8363</v>
+        <v>8459</v>
       </c>
       <c r="AD2" t="s">
-        <v>8386</v>
+        <v>8459</v>
       </c>
       <c r="AE2" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF2" t="s">
-        <v>8415</v>
+        <v>8459</v>
       </c>
       <c r="AG2" t="s">
-        <v>8438</v>
+        <v>8459</v>
       </c>
       <c r="AH2" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI2" t="s">
         <v>8463</v>
@@ -28215,100 +28215,100 @@
         <v>2009</v>
       </c>
       <c r="C3" t="s">
-        <v>7935</v>
+        <v>8459</v>
       </c>
       <c r="D3" t="s">
-        <v>7952</v>
+        <v>8459</v>
       </c>
       <c r="E3" t="s">
-        <v>7972</v>
+        <v>8459</v>
       </c>
       <c r="F3" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G3" t="s">
-        <v>7993</v>
+        <v>8459</v>
       </c>
       <c r="H3" t="s">
-        <v>8013</v>
+        <v>8459</v>
       </c>
       <c r="I3" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J3" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K3" t="s">
-        <v>8047</v>
+        <v>8459</v>
       </c>
       <c r="L3" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M3" t="s">
-        <v>8073</v>
+        <v>8459</v>
       </c>
       <c r="N3" t="s">
-        <v>8096</v>
+        <v>8459</v>
       </c>
       <c r="O3" t="s">
-        <v>8117</v>
+        <v>8459</v>
       </c>
       <c r="P3" t="s">
-        <v>8139</v>
+        <v>8459</v>
       </c>
       <c r="Q3" t="s">
-        <v>8162</v>
+        <v>8459</v>
       </c>
       <c r="R3" t="s">
-        <v>8184</v>
+        <v>8463</v>
       </c>
       <c r="S3" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T3" t="s">
-        <v>8202</v>
+        <v>8459</v>
       </c>
       <c r="U3" t="s">
-        <v>8222</v>
+        <v>8459</v>
       </c>
       <c r="V3" t="s">
-        <v>8242</v>
+        <v>8459</v>
       </c>
       <c r="W3" t="s">
-        <v>8264</v>
+        <v>8459</v>
       </c>
       <c r="X3" t="s">
-        <v>8286</v>
+        <v>8459</v>
       </c>
       <c r="Y3" t="s">
-        <v>8308</v>
+        <v>8459</v>
       </c>
       <c r="Z3" t="s">
-        <v>8331</v>
+        <v>8459</v>
       </c>
       <c r="AA3" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB3" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC3" t="s">
-        <v>8364</v>
+        <v>8459</v>
       </c>
       <c r="AD3" t="s">
-        <v>8387</v>
+        <v>8459</v>
       </c>
       <c r="AE3" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF3" t="s">
-        <v>8416</v>
+        <v>8459</v>
       </c>
       <c r="AG3" t="s">
-        <v>8439</v>
+        <v>8459</v>
       </c>
       <c r="AH3" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI3" t="s">
         <v>8463</v>
@@ -28322,100 +28322,100 @@
         <v>2008</v>
       </c>
       <c r="C4" t="s">
-        <v>7936</v>
+        <v>8463</v>
       </c>
       <c r="D4" t="s">
-        <v>7953</v>
+        <v>8463</v>
       </c>
       <c r="E4" t="s">
-        <v>7973</v>
+        <v>8463</v>
       </c>
       <c r="F4" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G4" t="s">
-        <v>7994</v>
+        <v>8463</v>
       </c>
       <c r="H4" t="s">
-        <v>8014</v>
+        <v>8463</v>
       </c>
       <c r="I4" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J4" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K4" t="s">
-        <v>8048</v>
+        <v>8463</v>
       </c>
       <c r="L4" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M4" t="s">
-        <v>8074</v>
+        <v>8459</v>
       </c>
       <c r="N4" t="s">
-        <v>8097</v>
+        <v>8463</v>
       </c>
       <c r="O4" t="s">
-        <v>8118</v>
+        <v>8459</v>
       </c>
       <c r="P4" t="s">
-        <v>8140</v>
+        <v>8459</v>
       </c>
       <c r="Q4" t="s">
-        <v>8163</v>
+        <v>8459</v>
       </c>
       <c r="R4" t="s">
-        <v>8184</v>
+        <v>8463</v>
       </c>
       <c r="S4" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T4" t="s">
-        <v>8203</v>
+        <v>8463</v>
       </c>
       <c r="U4" t="s">
-        <v>8223</v>
+        <v>8463</v>
       </c>
       <c r="V4" t="s">
-        <v>8243</v>
+        <v>8463</v>
       </c>
       <c r="W4" t="s">
-        <v>8265</v>
+        <v>8459</v>
       </c>
       <c r="X4" t="s">
-        <v>8287</v>
+        <v>8459</v>
       </c>
       <c r="Y4" t="s">
-        <v>8309</v>
+        <v>8463</v>
       </c>
       <c r="Z4" t="s">
-        <v>8332</v>
+        <v>8463</v>
       </c>
       <c r="AA4" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB4" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC4" t="s">
-        <v>8365</v>
+        <v>8459</v>
       </c>
       <c r="AD4" t="s">
-        <v>8388</v>
+        <v>8459</v>
       </c>
       <c r="AE4" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF4" t="s">
-        <v>8417</v>
+        <v>8459</v>
       </c>
       <c r="AG4" t="s">
-        <v>8440</v>
+        <v>8459</v>
       </c>
       <c r="AH4" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI4" t="s">
         <v>8463</v>
@@ -28429,100 +28429,100 @@
         <v>2013</v>
       </c>
       <c r="C5" t="s">
-        <v>7937</v>
+        <v>8459</v>
       </c>
       <c r="D5" t="s">
-        <v>7954</v>
+        <v>8459</v>
       </c>
       <c r="E5" t="s">
-        <v>7973</v>
+        <v>8463</v>
       </c>
       <c r="F5" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G5" t="s">
-        <v>7995</v>
+        <v>8459</v>
       </c>
       <c r="H5" t="s">
-        <v>8015</v>
+        <v>8459</v>
       </c>
       <c r="I5" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J5" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K5" t="s">
-        <v>8049</v>
+        <v>8459</v>
       </c>
       <c r="L5" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M5" t="s">
-        <v>8075</v>
+        <v>8459</v>
       </c>
       <c r="N5" t="s">
-        <v>8098</v>
+        <v>8459</v>
       </c>
       <c r="O5" t="s">
-        <v>8119</v>
+        <v>8459</v>
       </c>
       <c r="P5" t="s">
-        <v>8141</v>
+        <v>8459</v>
       </c>
       <c r="Q5" t="s">
-        <v>8164</v>
+        <v>8459</v>
       </c>
       <c r="R5" t="s">
-        <v>8184</v>
+        <v>8463</v>
       </c>
       <c r="S5" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T5" t="s">
-        <v>8204</v>
+        <v>8459</v>
       </c>
       <c r="U5" t="s">
-        <v>8224</v>
+        <v>8459</v>
       </c>
       <c r="V5" t="s">
-        <v>8244</v>
+        <v>8459</v>
       </c>
       <c r="W5" t="s">
-        <v>8266</v>
+        <v>8459</v>
       </c>
       <c r="X5" t="s">
-        <v>8288</v>
+        <v>8459</v>
       </c>
       <c r="Y5" t="s">
-        <v>8310</v>
+        <v>8459</v>
       </c>
       <c r="Z5" t="s">
-        <v>8333</v>
+        <v>8459</v>
       </c>
       <c r="AA5" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB5" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC5" t="s">
-        <v>8366</v>
+        <v>8459</v>
       </c>
       <c r="AD5" t="s">
-        <v>8389</v>
+        <v>8463</v>
       </c>
       <c r="AE5" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF5" t="s">
-        <v>8418</v>
+        <v>8459</v>
       </c>
       <c r="AG5" t="s">
-        <v>8441</v>
+        <v>8459</v>
       </c>
       <c r="AH5" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI5" t="s">
         <v>8463</v>
@@ -28536,100 +28536,100 @@
         <v>2010</v>
       </c>
       <c r="C6" t="s">
-        <v>7938</v>
+        <v>8463</v>
       </c>
       <c r="D6" t="s">
-        <v>7955</v>
+        <v>8463</v>
       </c>
       <c r="E6" t="s">
-        <v>7973</v>
+        <v>8463</v>
       </c>
       <c r="F6" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G6" t="s">
-        <v>7996</v>
+        <v>8463</v>
       </c>
       <c r="H6" t="s">
-        <v>8016</v>
+        <v>8459</v>
       </c>
       <c r="I6" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J6" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K6" t="s">
-        <v>8050</v>
+        <v>8463</v>
       </c>
       <c r="L6" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M6" t="s">
-        <v>8076</v>
+        <v>8459</v>
       </c>
       <c r="N6" t="s">
-        <v>8099</v>
+        <v>8463</v>
       </c>
       <c r="O6" t="s">
-        <v>8120</v>
+        <v>8459</v>
       </c>
       <c r="P6" t="s">
-        <v>8142</v>
+        <v>8459</v>
       </c>
       <c r="Q6" t="s">
-        <v>8165</v>
+        <v>8459</v>
       </c>
       <c r="R6" t="s">
-        <v>8184</v>
+        <v>8463</v>
       </c>
       <c r="S6" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T6" t="s">
-        <v>8205</v>
+        <v>8463</v>
       </c>
       <c r="U6" t="s">
-        <v>8225</v>
+        <v>8463</v>
       </c>
       <c r="V6" t="s">
-        <v>8245</v>
+        <v>8459</v>
       </c>
       <c r="W6" t="s">
-        <v>8267</v>
+        <v>8463</v>
       </c>
       <c r="X6" t="s">
-        <v>8289</v>
+        <v>8463</v>
       </c>
       <c r="Y6" t="s">
-        <v>8311</v>
+        <v>8459</v>
       </c>
       <c r="Z6" t="s">
-        <v>8334</v>
+        <v>8463</v>
       </c>
       <c r="AA6" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB6" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC6" t="s">
-        <v>8367</v>
+        <v>8459</v>
       </c>
       <c r="AD6" t="s">
-        <v>8390</v>
+        <v>8459</v>
       </c>
       <c r="AE6" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF6" t="s">
-        <v>8419</v>
+        <v>8459</v>
       </c>
       <c r="AG6" t="s">
-        <v>8442</v>
+        <v>8459</v>
       </c>
       <c r="AH6" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI6" t="s">
         <v>8463</v>
@@ -28643,100 +28643,100 @@
         <v>2014</v>
       </c>
       <c r="C7" t="s">
-        <v>7938</v>
+        <v>8463</v>
       </c>
       <c r="D7" t="s">
-        <v>7955</v>
+        <v>8463</v>
       </c>
       <c r="E7" t="s">
-        <v>7973</v>
+        <v>8463</v>
       </c>
       <c r="F7" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G7" t="s">
-        <v>7996</v>
+        <v>8463</v>
       </c>
       <c r="H7" t="s">
-        <v>8017</v>
+        <v>8459</v>
       </c>
       <c r="I7" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J7" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K7" t="s">
-        <v>8050</v>
+        <v>8463</v>
       </c>
       <c r="L7" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M7" t="s">
-        <v>8077</v>
+        <v>8459</v>
       </c>
       <c r="N7" t="s">
-        <v>8099</v>
+        <v>8463</v>
       </c>
       <c r="O7" t="s">
-        <v>8121</v>
+        <v>8459</v>
       </c>
       <c r="P7" t="s">
-        <v>8143</v>
+        <v>8459</v>
       </c>
       <c r="Q7" t="s">
-        <v>8166</v>
+        <v>8459</v>
       </c>
       <c r="R7" t="s">
-        <v>8184</v>
+        <v>8463</v>
       </c>
       <c r="S7" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T7" t="s">
-        <v>8205</v>
+        <v>8463</v>
       </c>
       <c r="U7" t="s">
-        <v>8225</v>
+        <v>8463</v>
       </c>
       <c r="V7" t="s">
-        <v>8246</v>
+        <v>8459</v>
       </c>
       <c r="W7" t="s">
-        <v>8267</v>
+        <v>8463</v>
       </c>
       <c r="X7" t="s">
-        <v>8289</v>
+        <v>8463</v>
       </c>
       <c r="Y7" t="s">
-        <v>8312</v>
+        <v>8459</v>
       </c>
       <c r="Z7" t="s">
-        <v>8334</v>
+        <v>8463</v>
       </c>
       <c r="AA7" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB7" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC7" t="s">
-        <v>8368</v>
+        <v>8459</v>
       </c>
       <c r="AD7" t="s">
-        <v>8391</v>
+        <v>8459</v>
       </c>
       <c r="AE7" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF7" t="s">
-        <v>8420</v>
+        <v>8459</v>
       </c>
       <c r="AG7" t="s">
-        <v>8443</v>
+        <v>8459</v>
       </c>
       <c r="AH7" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI7" t="s">
         <v>8463</v>
@@ -28750,100 +28750,100 @@
         <v>2010</v>
       </c>
       <c r="C8" t="s">
-        <v>7938</v>
+        <v>8463</v>
       </c>
       <c r="D8" t="s">
-        <v>7956</v>
+        <v>8459</v>
       </c>
       <c r="E8" t="s">
-        <v>7974</v>
+        <v>8459</v>
       </c>
       <c r="F8" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G8" t="s">
-        <v>7997</v>
+        <v>8459</v>
       </c>
       <c r="H8" t="s">
-        <v>8018</v>
+        <v>8459</v>
       </c>
       <c r="I8" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J8" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K8" t="s">
-        <v>8051</v>
+        <v>8459</v>
       </c>
       <c r="L8" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M8" t="s">
-        <v>8078</v>
+        <v>8459</v>
       </c>
       <c r="N8" t="s">
-        <v>8100</v>
+        <v>8459</v>
       </c>
       <c r="O8" t="s">
-        <v>8122</v>
+        <v>8459</v>
       </c>
       <c r="P8" t="s">
-        <v>8144</v>
+        <v>8459</v>
       </c>
       <c r="Q8" t="s">
-        <v>8167</v>
+        <v>8459</v>
       </c>
       <c r="R8" t="s">
-        <v>8185</v>
+        <v>8459</v>
       </c>
       <c r="S8" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T8" t="s">
-        <v>8206</v>
+        <v>8459</v>
       </c>
       <c r="U8" t="s">
-        <v>8226</v>
+        <v>8459</v>
       </c>
       <c r="V8" t="s">
-        <v>8247</v>
+        <v>8459</v>
       </c>
       <c r="W8" t="s">
-        <v>8268</v>
+        <v>8459</v>
       </c>
       <c r="X8" t="s">
-        <v>8290</v>
+        <v>8459</v>
       </c>
       <c r="Y8" t="s">
-        <v>8313</v>
+        <v>8459</v>
       </c>
       <c r="Z8" t="s">
-        <v>8335</v>
+        <v>8459</v>
       </c>
       <c r="AA8" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB8" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC8" t="s">
-        <v>8369</v>
+        <v>8463</v>
       </c>
       <c r="AD8" t="s">
-        <v>8392</v>
+        <v>8459</v>
       </c>
       <c r="AE8" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF8" t="s">
-        <v>8421</v>
+        <v>8459</v>
       </c>
       <c r="AG8" t="s">
-        <v>8444</v>
+        <v>8459</v>
       </c>
       <c r="AH8" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI8" t="s">
         <v>8463</v>
@@ -28857,100 +28857,100 @@
         <v>2013</v>
       </c>
       <c r="C9" t="s">
-        <v>7939</v>
+        <v>8459</v>
       </c>
       <c r="D9" t="s">
-        <v>7957</v>
+        <v>8459</v>
       </c>
       <c r="E9" t="s">
-        <v>7975</v>
+        <v>8459</v>
       </c>
       <c r="F9" t="s">
-        <v>7986</v>
+        <v>8463</v>
       </c>
       <c r="G9" t="s">
-        <v>7998</v>
+        <v>8463</v>
       </c>
       <c r="H9" t="s">
-        <v>8019</v>
+        <v>8459</v>
       </c>
       <c r="I9" t="s">
-        <v>8034</v>
+        <v>8463</v>
       </c>
       <c r="J9" t="s">
-        <v>8040</v>
+        <v>8463</v>
       </c>
       <c r="K9" t="s">
-        <v>8052</v>
+        <v>8463</v>
       </c>
       <c r="L9" t="s">
-        <v>8066</v>
+        <v>8463</v>
       </c>
       <c r="M9" t="s">
-        <v>8079</v>
+        <v>8459</v>
       </c>
       <c r="N9" t="s">
-        <v>8101</v>
+        <v>8463</v>
       </c>
       <c r="O9" t="s">
-        <v>8123</v>
+        <v>8459</v>
       </c>
       <c r="P9" t="s">
-        <v>8145</v>
+        <v>8459</v>
       </c>
       <c r="Q9" t="s">
-        <v>8168</v>
+        <v>8459</v>
       </c>
       <c r="R9" t="s">
-        <v>8186</v>
+        <v>8463</v>
       </c>
       <c r="S9" t="s">
-        <v>8195</v>
+        <v>8463</v>
       </c>
       <c r="T9" t="s">
-        <v>8207</v>
+        <v>8463</v>
       </c>
       <c r="U9" t="s">
-        <v>8227</v>
+        <v>8463</v>
       </c>
       <c r="V9" t="s">
-        <v>8248</v>
+        <v>8459</v>
       </c>
       <c r="W9" t="s">
-        <v>8269</v>
+        <v>8463</v>
       </c>
       <c r="X9" t="s">
-        <v>8291</v>
+        <v>8463</v>
       </c>
       <c r="Y9" t="s">
-        <v>8314</v>
+        <v>8459</v>
       </c>
       <c r="Z9" t="s">
-        <v>8336</v>
+        <v>8463</v>
       </c>
       <c r="AA9" t="s">
-        <v>8351</v>
+        <v>8463</v>
       </c>
       <c r="AB9" t="s">
-        <v>8357</v>
+        <v>8463</v>
       </c>
       <c r="AC9" t="s">
-        <v>8370</v>
+        <v>8459</v>
       </c>
       <c r="AD9" t="s">
-        <v>8393</v>
+        <v>8459</v>
       </c>
       <c r="AE9" t="s">
-        <v>8409</v>
+        <v>8463</v>
       </c>
       <c r="AF9" t="s">
-        <v>8422</v>
+        <v>8459</v>
       </c>
       <c r="AG9" t="s">
-        <v>8445</v>
+        <v>8459</v>
       </c>
       <c r="AH9" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI9" t="s">
         <v>8463</v>
@@ -28964,100 +28964,100 @@
         <v>2011</v>
       </c>
       <c r="C10" t="s">
-        <v>7940</v>
+        <v>8459</v>
       </c>
       <c r="D10" t="s">
-        <v>7958</v>
+        <v>8459</v>
       </c>
       <c r="E10" t="s">
-        <v>7976</v>
+        <v>8459</v>
       </c>
       <c r="F10" t="s">
-        <v>7987</v>
+        <v>8459</v>
       </c>
       <c r="G10" t="s">
-        <v>7999</v>
+        <v>8459</v>
       </c>
       <c r="H10" t="s">
-        <v>8020</v>
+        <v>8459</v>
       </c>
       <c r="I10" t="s">
-        <v>8035</v>
+        <v>8459</v>
       </c>
       <c r="J10" t="s">
-        <v>8041</v>
+        <v>8459</v>
       </c>
       <c r="K10" t="s">
-        <v>8053</v>
+        <v>8459</v>
       </c>
       <c r="L10" t="s">
-        <v>8067</v>
+        <v>8459</v>
       </c>
       <c r="M10" t="s">
-        <v>8080</v>
+        <v>8459</v>
       </c>
       <c r="N10" t="s">
-        <v>8102</v>
+        <v>8459</v>
       </c>
       <c r="O10" t="s">
-        <v>8124</v>
+        <v>8459</v>
       </c>
       <c r="P10" t="s">
-        <v>8146</v>
+        <v>8459</v>
       </c>
       <c r="Q10" t="s">
-        <v>8169</v>
+        <v>8459</v>
       </c>
       <c r="R10" t="s">
-        <v>8187</v>
+        <v>8459</v>
       </c>
       <c r="S10" t="s">
-        <v>8196</v>
+        <v>8459</v>
       </c>
       <c r="T10" t="s">
-        <v>8208</v>
+        <v>8459</v>
       </c>
       <c r="U10" t="s">
-        <v>8228</v>
+        <v>8459</v>
       </c>
       <c r="V10" t="s">
-        <v>8249</v>
+        <v>8459</v>
       </c>
       <c r="W10" t="s">
-        <v>8270</v>
+        <v>8459</v>
       </c>
       <c r="X10" t="s">
-        <v>8292</v>
+        <v>8459</v>
       </c>
       <c r="Y10" t="s">
-        <v>8315</v>
+        <v>8459</v>
       </c>
       <c r="Z10" t="s">
-        <v>8337</v>
+        <v>8459</v>
       </c>
       <c r="AA10" t="s">
-        <v>8352</v>
+        <v>8459</v>
       </c>
       <c r="AB10" t="s">
-        <v>8358</v>
+        <v>8459</v>
       </c>
       <c r="AC10" t="s">
-        <v>8371</v>
+        <v>8459</v>
       </c>
       <c r="AD10" t="s">
-        <v>8394</v>
+        <v>8459</v>
       </c>
       <c r="AE10" t="s">
-        <v>8410</v>
+        <v>8459</v>
       </c>
       <c r="AF10" t="s">
-        <v>8423</v>
+        <v>8459</v>
       </c>
       <c r="AG10" t="s">
-        <v>8446</v>
+        <v>8459</v>
       </c>
       <c r="AH10" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI10" t="s">
         <v>8463</v>
@@ -29071,100 +29071,100 @@
         <v>2011</v>
       </c>
       <c r="C11" t="s">
-        <v>7941</v>
+        <v>8459</v>
       </c>
       <c r="D11" t="s">
-        <v>7959</v>
+        <v>8459</v>
       </c>
       <c r="E11" t="s">
-        <v>7977</v>
+        <v>8459</v>
       </c>
       <c r="F11" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G11" t="s">
-        <v>8000</v>
+        <v>8459</v>
       </c>
       <c r="H11" t="s">
-        <v>8021</v>
+        <v>8463</v>
       </c>
       <c r="I11" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J11" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K11" t="s">
-        <v>8054</v>
+        <v>8463</v>
       </c>
       <c r="L11" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M11" t="s">
-        <v>8081</v>
+        <v>8459</v>
       </c>
       <c r="N11" t="s">
-        <v>8103</v>
+        <v>8463</v>
       </c>
       <c r="O11" t="s">
-        <v>8125</v>
+        <v>8459</v>
       </c>
       <c r="P11" t="s">
-        <v>8147</v>
+        <v>8459</v>
       </c>
       <c r="Q11" t="s">
-        <v>8170</v>
+        <v>8459</v>
       </c>
       <c r="R11" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S11" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T11" t="s">
-        <v>8209</v>
+        <v>8463</v>
       </c>
       <c r="U11" t="s">
-        <v>8229</v>
+        <v>8463</v>
       </c>
       <c r="V11" t="s">
-        <v>8250</v>
+        <v>8459</v>
       </c>
       <c r="W11" t="s">
-        <v>8271</v>
+        <v>8459</v>
       </c>
       <c r="X11" t="s">
-        <v>8293</v>
+        <v>8463</v>
       </c>
       <c r="Y11" t="s">
-        <v>8316</v>
+        <v>8459</v>
       </c>
       <c r="Z11" t="s">
-        <v>8338</v>
+        <v>8463</v>
       </c>
       <c r="AA11" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB11" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC11" t="s">
-        <v>8372</v>
+        <v>8459</v>
       </c>
       <c r="AD11" t="s">
-        <v>8395</v>
+        <v>8459</v>
       </c>
       <c r="AE11" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF11" t="s">
-        <v>8424</v>
+        <v>8459</v>
       </c>
       <c r="AG11" t="s">
-        <v>8447</v>
+        <v>8459</v>
       </c>
       <c r="AH11" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI11" t="s">
         <v>8463</v>
@@ -29178,100 +29178,100 @@
         <v>2011</v>
       </c>
       <c r="C12" t="s">
-        <v>7942</v>
+        <v>8459</v>
       </c>
       <c r="D12" t="s">
-        <v>7960</v>
+        <v>8459</v>
       </c>
       <c r="E12" t="s">
-        <v>7978</v>
+        <v>8463</v>
       </c>
       <c r="F12" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G12" t="s">
-        <v>8001</v>
+        <v>8459</v>
       </c>
       <c r="H12" t="s">
-        <v>8022</v>
+        <v>8459</v>
       </c>
       <c r="I12" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J12" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K12" t="s">
-        <v>8055</v>
+        <v>8459</v>
       </c>
       <c r="L12" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M12" t="s">
-        <v>8082</v>
+        <v>8459</v>
       </c>
       <c r="N12" t="s">
-        <v>8104</v>
+        <v>8459</v>
       </c>
       <c r="O12" t="s">
-        <v>8126</v>
+        <v>8459</v>
       </c>
       <c r="P12" t="s">
-        <v>8148</v>
+        <v>8459</v>
       </c>
       <c r="Q12" t="s">
-        <v>8171</v>
+        <v>8459</v>
       </c>
       <c r="R12" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S12" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T12" t="s">
-        <v>8210</v>
+        <v>8459</v>
       </c>
       <c r="U12" t="s">
-        <v>8230</v>
+        <v>8459</v>
       </c>
       <c r="V12" t="s">
-        <v>8251</v>
+        <v>8459</v>
       </c>
       <c r="W12" t="s">
-        <v>8272</v>
+        <v>8459</v>
       </c>
       <c r="X12" t="s">
-        <v>8294</v>
+        <v>8459</v>
       </c>
       <c r="Y12" t="s">
-        <v>8317</v>
+        <v>8459</v>
       </c>
       <c r="Z12" t="s">
-        <v>8339</v>
+        <v>8459</v>
       </c>
       <c r="AA12" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB12" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC12" t="s">
-        <v>8373</v>
+        <v>8459</v>
       </c>
       <c r="AD12" t="s">
-        <v>8396</v>
+        <v>8459</v>
       </c>
       <c r="AE12" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF12" t="s">
-        <v>8425</v>
+        <v>8459</v>
       </c>
       <c r="AG12" t="s">
-        <v>8448</v>
+        <v>8459</v>
       </c>
       <c r="AH12" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI12" t="s">
         <v>8463</v>
@@ -29285,100 +29285,100 @@
         <v>2011</v>
       </c>
       <c r="C13" t="s">
-        <v>7943</v>
+        <v>8463</v>
       </c>
       <c r="D13" t="s">
-        <v>7961</v>
+        <v>8459</v>
       </c>
       <c r="E13" t="s">
-        <v>7979</v>
+        <v>8459</v>
       </c>
       <c r="F13" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G13" t="s">
-        <v>8002</v>
+        <v>8459</v>
       </c>
       <c r="H13" t="s">
-        <v>8023</v>
+        <v>8459</v>
       </c>
       <c r="I13" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J13" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K13" t="s">
-        <v>8056</v>
+        <v>8459</v>
       </c>
       <c r="L13" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M13" t="s">
-        <v>8083</v>
+        <v>8459</v>
       </c>
       <c r="N13" t="s">
-        <v>8105</v>
+        <v>8459</v>
       </c>
       <c r="O13" t="s">
-        <v>8127</v>
+        <v>8459</v>
       </c>
       <c r="P13" t="s">
-        <v>8149</v>
+        <v>8459</v>
       </c>
       <c r="Q13" t="s">
-        <v>8172</v>
+        <v>8459</v>
       </c>
       <c r="R13" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S13" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T13" t="s">
-        <v>8211</v>
+        <v>8459</v>
       </c>
       <c r="U13" t="s">
-        <v>8231</v>
+        <v>8459</v>
       </c>
       <c r="V13" t="s">
-        <v>8252</v>
+        <v>8459</v>
       </c>
       <c r="W13" t="s">
-        <v>8273</v>
+        <v>8459</v>
       </c>
       <c r="X13" t="s">
-        <v>8295</v>
+        <v>8459</v>
       </c>
       <c r="Y13" t="s">
-        <v>8318</v>
+        <v>8459</v>
       </c>
       <c r="Z13" t="s">
-        <v>8340</v>
+        <v>8459</v>
       </c>
       <c r="AA13" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB13" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC13" t="s">
-        <v>8374</v>
+        <v>8459</v>
       </c>
       <c r="AD13" t="s">
-        <v>8397</v>
+        <v>8459</v>
       </c>
       <c r="AE13" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF13" t="s">
-        <v>8426</v>
+        <v>8459</v>
       </c>
       <c r="AG13" t="s">
-        <v>8449</v>
+        <v>8459</v>
       </c>
       <c r="AH13" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI13" t="s">
         <v>8463</v>
@@ -29392,100 +29392,100 @@
         <v>2010</v>
       </c>
       <c r="C14" t="s">
-        <v>7944</v>
+        <v>8459</v>
       </c>
       <c r="D14" t="s">
-        <v>7962</v>
+        <v>8459</v>
       </c>
       <c r="E14" t="s">
-        <v>7980</v>
+        <v>8463</v>
       </c>
       <c r="F14" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G14" t="s">
-        <v>8003</v>
+        <v>8459</v>
       </c>
       <c r="H14" t="s">
-        <v>8024</v>
+        <v>8459</v>
       </c>
       <c r="I14" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J14" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K14" t="s">
-        <v>8057</v>
+        <v>8459</v>
       </c>
       <c r="L14" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M14" t="s">
-        <v>8084</v>
+        <v>8459</v>
       </c>
       <c r="N14" t="s">
-        <v>8106</v>
+        <v>8459</v>
       </c>
       <c r="O14" t="s">
-        <v>8128</v>
+        <v>8459</v>
       </c>
       <c r="P14" t="s">
-        <v>8150</v>
+        <v>8459</v>
       </c>
       <c r="Q14" t="s">
-        <v>8173</v>
+        <v>8459</v>
       </c>
       <c r="R14" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S14" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T14" t="s">
-        <v>8212</v>
+        <v>8459</v>
       </c>
       <c r="U14" t="s">
-        <v>8232</v>
+        <v>8459</v>
       </c>
       <c r="V14" t="s">
-        <v>8253</v>
+        <v>8459</v>
       </c>
       <c r="W14" t="s">
-        <v>8274</v>
+        <v>8459</v>
       </c>
       <c r="X14" t="s">
-        <v>8296</v>
+        <v>8459</v>
       </c>
       <c r="Y14" t="s">
-        <v>8319</v>
+        <v>8459</v>
       </c>
       <c r="Z14" t="s">
-        <v>8341</v>
+        <v>8459</v>
       </c>
       <c r="AA14" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB14" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC14" t="s">
-        <v>8375</v>
+        <v>8463</v>
       </c>
       <c r="AD14" t="s">
-        <v>8398</v>
+        <v>8459</v>
       </c>
       <c r="AE14" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF14" t="s">
-        <v>8427</v>
+        <v>8459</v>
       </c>
       <c r="AG14" t="s">
-        <v>8450</v>
+        <v>8459</v>
       </c>
       <c r="AH14" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI14" t="s">
         <v>8463</v>
@@ -29499,100 +29499,100 @@
         <v>2012</v>
       </c>
       <c r="C15" t="s">
-        <v>7945</v>
+        <v>8463</v>
       </c>
       <c r="D15" t="s">
-        <v>7963</v>
+        <v>8463</v>
       </c>
       <c r="E15" t="s">
-        <v>7980</v>
+        <v>8463</v>
       </c>
       <c r="F15" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G15" t="s">
-        <v>8004</v>
+        <v>8463</v>
       </c>
       <c r="H15" t="s">
-        <v>8025</v>
+        <v>8463</v>
       </c>
       <c r="I15" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J15" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K15" t="s">
-        <v>8058</v>
+        <v>8463</v>
       </c>
       <c r="L15" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M15" t="s">
-        <v>8085</v>
+        <v>8463</v>
       </c>
       <c r="N15" t="s">
-        <v>8107</v>
+        <v>8463</v>
       </c>
       <c r="O15" t="s">
-        <v>8129</v>
+        <v>8463</v>
       </c>
       <c r="P15" t="s">
-        <v>8151</v>
+        <v>8459</v>
       </c>
       <c r="Q15" t="s">
-        <v>8174</v>
+        <v>8459</v>
       </c>
       <c r="R15" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S15" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T15" t="s">
-        <v>8213</v>
+        <v>8463</v>
       </c>
       <c r="U15" t="s">
-        <v>8233</v>
+        <v>8463</v>
       </c>
       <c r="V15" t="s">
-        <v>8254</v>
+        <v>8463</v>
       </c>
       <c r="W15" t="s">
-        <v>8275</v>
+        <v>8459</v>
       </c>
       <c r="X15" t="s">
-        <v>8297</v>
+        <v>8459</v>
       </c>
       <c r="Y15" t="s">
-        <v>8320</v>
+        <v>8459</v>
       </c>
       <c r="Z15" t="s">
-        <v>8342</v>
+        <v>8463</v>
       </c>
       <c r="AA15" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB15" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC15" t="s">
-        <v>8376</v>
+        <v>8459</v>
       </c>
       <c r="AD15" t="s">
-        <v>8399</v>
+        <v>8459</v>
       </c>
       <c r="AE15" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF15" t="s">
-        <v>8428</v>
+        <v>8459</v>
       </c>
       <c r="AG15" t="s">
-        <v>8451</v>
+        <v>8459</v>
       </c>
       <c r="AH15" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI15" t="s">
         <v>8463</v>
@@ -29606,100 +29606,100 @@
         <v>2014</v>
       </c>
       <c r="C16" t="s">
-        <v>7945</v>
+        <v>8463</v>
       </c>
       <c r="D16" t="s">
-        <v>7963</v>
+        <v>8463</v>
       </c>
       <c r="E16" t="s">
-        <v>7980</v>
+        <v>8463</v>
       </c>
       <c r="F16" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G16" t="s">
-        <v>8004</v>
+        <v>8463</v>
       </c>
       <c r="H16" t="s">
-        <v>8025</v>
+        <v>8463</v>
       </c>
       <c r="I16" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J16" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K16" t="s">
-        <v>8058</v>
+        <v>8463</v>
       </c>
       <c r="L16" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M16" t="s">
-        <v>8086</v>
+        <v>8459</v>
       </c>
       <c r="N16" t="s">
-        <v>8107</v>
+        <v>8463</v>
       </c>
       <c r="O16" t="s">
-        <v>8129</v>
+        <v>8463</v>
       </c>
       <c r="P16" t="s">
-        <v>8152</v>
+        <v>8459</v>
       </c>
       <c r="Q16" t="s">
-        <v>8175</v>
+        <v>8459</v>
       </c>
       <c r="R16" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S16" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T16" t="s">
-        <v>8213</v>
+        <v>8463</v>
       </c>
       <c r="U16" t="s">
-        <v>8233</v>
+        <v>8463</v>
       </c>
       <c r="V16" t="s">
-        <v>8254</v>
+        <v>8463</v>
       </c>
       <c r="W16" t="s">
-        <v>8276</v>
+        <v>8459</v>
       </c>
       <c r="X16" t="s">
-        <v>8298</v>
+        <v>8459</v>
       </c>
       <c r="Y16" t="s">
-        <v>8321</v>
+        <v>8459</v>
       </c>
       <c r="Z16" t="s">
-        <v>8342</v>
+        <v>8463</v>
       </c>
       <c r="AA16" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB16" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC16" t="s">
-        <v>8377</v>
+        <v>8459</v>
       </c>
       <c r="AD16" t="s">
-        <v>8400</v>
+        <v>8459</v>
       </c>
       <c r="AE16" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF16" t="s">
-        <v>8429</v>
+        <v>8459</v>
       </c>
       <c r="AG16" t="s">
-        <v>8452</v>
+        <v>8459</v>
       </c>
       <c r="AH16" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI16" t="s">
         <v>8463</v>
@@ -29713,100 +29713,100 @@
         <v>2009</v>
       </c>
       <c r="C17" t="s">
-        <v>7946</v>
+        <v>8459</v>
       </c>
       <c r="D17" t="s">
-        <v>7964</v>
+        <v>8459</v>
       </c>
       <c r="E17" t="s">
-        <v>7980</v>
+        <v>8463</v>
       </c>
       <c r="F17" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G17" t="s">
-        <v>8005</v>
+        <v>8459</v>
       </c>
       <c r="H17" t="s">
-        <v>8026</v>
+        <v>8459</v>
       </c>
       <c r="I17" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J17" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K17" t="s">
-        <v>8059</v>
+        <v>8459</v>
       </c>
       <c r="L17" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M17" t="s">
-        <v>8087</v>
+        <v>8459</v>
       </c>
       <c r="N17" t="s">
-        <v>8108</v>
+        <v>8459</v>
       </c>
       <c r="O17" t="s">
-        <v>8130</v>
+        <v>8459</v>
       </c>
       <c r="P17" t="s">
-        <v>8153</v>
+        <v>8459</v>
       </c>
       <c r="Q17" t="s">
-        <v>8176</v>
+        <v>8459</v>
       </c>
       <c r="R17" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S17" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T17" t="s">
-        <v>8214</v>
+        <v>8459</v>
       </c>
       <c r="U17" t="s">
-        <v>8234</v>
+        <v>8459</v>
       </c>
       <c r="V17" t="s">
-        <v>8255</v>
+        <v>8459</v>
       </c>
       <c r="W17" t="s">
-        <v>8277</v>
+        <v>8459</v>
       </c>
       <c r="X17" t="s">
-        <v>8299</v>
+        <v>8459</v>
       </c>
       <c r="Y17" t="s">
-        <v>8322</v>
+        <v>8459</v>
       </c>
       <c r="Z17" t="s">
-        <v>8343</v>
+        <v>8459</v>
       </c>
       <c r="AA17" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB17" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC17" t="s">
-        <v>8378</v>
+        <v>8459</v>
       </c>
       <c r="AD17" t="s">
-        <v>8401</v>
+        <v>8459</v>
       </c>
       <c r="AE17" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF17" t="s">
-        <v>8430</v>
+        <v>8459</v>
       </c>
       <c r="AG17" t="s">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="AH17" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI17" t="s">
         <v>8463</v>
@@ -29820,100 +29820,100 @@
         <v>2016</v>
       </c>
       <c r="C18" t="s">
-        <v>7947</v>
+        <v>8463</v>
       </c>
       <c r="D18" t="s">
-        <v>7965</v>
+        <v>8463</v>
       </c>
       <c r="E18" t="s">
-        <v>7980</v>
+        <v>8463</v>
       </c>
       <c r="F18" t="s">
-        <v>7988</v>
+        <v>8463</v>
       </c>
       <c r="G18" t="s">
-        <v>8006</v>
+        <v>8463</v>
       </c>
       <c r="H18" t="s">
-        <v>8027</v>
+        <v>8463</v>
       </c>
       <c r="I18" t="s">
-        <v>8036</v>
+        <v>8463</v>
       </c>
       <c r="J18" t="s">
-        <v>8042</v>
+        <v>8463</v>
       </c>
       <c r="K18" t="s">
-        <v>8060</v>
+        <v>8463</v>
       </c>
       <c r="L18" t="s">
-        <v>8068</v>
+        <v>8463</v>
       </c>
       <c r="M18" t="s">
-        <v>8088</v>
+        <v>8463</v>
       </c>
       <c r="N18" t="s">
-        <v>8109</v>
+        <v>8463</v>
       </c>
       <c r="O18" t="s">
-        <v>8131</v>
+        <v>8459</v>
       </c>
       <c r="P18" t="s">
-        <v>8154</v>
+        <v>8459</v>
       </c>
       <c r="Q18" t="s">
-        <v>8177</v>
+        <v>8463</v>
       </c>
       <c r="R18" t="s">
-        <v>8188</v>
+        <v>8463</v>
       </c>
       <c r="S18" t="s">
-        <v>8197</v>
+        <v>8463</v>
       </c>
       <c r="T18" t="s">
-        <v>8215</v>
+        <v>8463</v>
       </c>
       <c r="U18" t="s">
-        <v>8235</v>
+        <v>8463</v>
       </c>
       <c r="V18" t="s">
-        <v>8256</v>
+        <v>8463</v>
       </c>
       <c r="W18" t="s">
-        <v>8278</v>
+        <v>8459</v>
       </c>
       <c r="X18" t="s">
-        <v>8300</v>
+        <v>8459</v>
       </c>
       <c r="Y18" t="s">
-        <v>8323</v>
+        <v>8459</v>
       </c>
       <c r="Z18" t="s">
-        <v>8344</v>
+        <v>8463</v>
       </c>
       <c r="AA18" t="s">
-        <v>8353</v>
+        <v>8463</v>
       </c>
       <c r="AB18" t="s">
-        <v>8359</v>
+        <v>8463</v>
       </c>
       <c r="AC18" t="s">
-        <v>8379</v>
+        <v>8459</v>
       </c>
       <c r="AD18" t="s">
-        <v>8402</v>
+        <v>8459</v>
       </c>
       <c r="AE18" t="s">
-        <v>8411</v>
+        <v>8463</v>
       </c>
       <c r="AF18" t="s">
-        <v>8431</v>
+        <v>8459</v>
       </c>
       <c r="AG18" t="s">
-        <v>8454</v>
+        <v>8459</v>
       </c>
       <c r="AH18" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI18" t="s">
         <v>8463</v>
@@ -29927,100 +29927,100 @@
         <v>2014</v>
       </c>
       <c r="C19" t="s">
-        <v>7948</v>
+        <v>8459</v>
       </c>
       <c r="D19" t="s">
-        <v>7966</v>
+        <v>8459</v>
       </c>
       <c r="E19" t="s">
-        <v>7981</v>
+        <v>8459</v>
       </c>
       <c r="F19" t="s">
-        <v>7989</v>
+        <v>8459</v>
       </c>
       <c r="G19" t="s">
-        <v>8007</v>
+        <v>8459</v>
       </c>
       <c r="H19" t="s">
-        <v>8028</v>
+        <v>8459</v>
       </c>
       <c r="I19" t="s">
-        <v>8037</v>
+        <v>8459</v>
       </c>
       <c r="J19" t="s">
-        <v>8043</v>
+        <v>8459</v>
       </c>
       <c r="K19" t="s">
-        <v>8061</v>
+        <v>8459</v>
       </c>
       <c r="L19" t="s">
-        <v>8069</v>
+        <v>8459</v>
       </c>
       <c r="M19" t="s">
-        <v>8089</v>
+        <v>8459</v>
       </c>
       <c r="N19" t="s">
-        <v>8110</v>
+        <v>8459</v>
       </c>
       <c r="O19" t="s">
-        <v>8132</v>
+        <v>8459</v>
       </c>
       <c r="P19" t="s">
-        <v>8155</v>
+        <v>8459</v>
       </c>
       <c r="Q19" t="s">
-        <v>8178</v>
+        <v>8459</v>
       </c>
       <c r="R19" t="s">
-        <v>8189</v>
+        <v>8459</v>
       </c>
       <c r="S19" t="s">
-        <v>8198</v>
+        <v>8459</v>
       </c>
       <c r="T19" t="s">
-        <v>8216</v>
+        <v>8459</v>
       </c>
       <c r="U19" t="s">
-        <v>8236</v>
+        <v>8459</v>
       </c>
       <c r="V19" t="s">
-        <v>8257</v>
+        <v>8459</v>
       </c>
       <c r="W19" t="s">
-        <v>8279</v>
+        <v>8459</v>
       </c>
       <c r="X19" t="s">
-        <v>8301</v>
+        <v>8459</v>
       </c>
       <c r="Y19" t="s">
-        <v>8324</v>
+        <v>8459</v>
       </c>
       <c r="Z19" t="s">
-        <v>8345</v>
+        <v>8459</v>
       </c>
       <c r="AA19" t="s">
-        <v>8354</v>
+        <v>8459</v>
       </c>
       <c r="AB19" t="s">
-        <v>8360</v>
+        <v>8459</v>
       </c>
       <c r="AC19" t="s">
-        <v>8380</v>
+        <v>8459</v>
       </c>
       <c r="AD19" t="s">
-        <v>8403</v>
+        <v>8459</v>
       </c>
       <c r="AE19" t="s">
-        <v>8412</v>
+        <v>8459</v>
       </c>
       <c r="AF19" t="s">
-        <v>8432</v>
+        <v>8459</v>
       </c>
       <c r="AG19" t="s">
-        <v>8455</v>
+        <v>8459</v>
       </c>
       <c r="AH19" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI19" t="s">
         <v>8463</v>
@@ -30034,100 +30034,100 @@
         <v>2009</v>
       </c>
       <c r="C20" t="s">
-        <v>7949</v>
+        <v>8463</v>
       </c>
       <c r="D20" t="s">
-        <v>7967</v>
+        <v>8459</v>
       </c>
       <c r="E20" t="s">
-        <v>7982</v>
+        <v>8459</v>
       </c>
       <c r="F20" t="s">
-        <v>7990</v>
+        <v>8463</v>
       </c>
       <c r="G20" t="s">
-        <v>8008</v>
+        <v>8459</v>
       </c>
       <c r="H20" t="s">
-        <v>8029</v>
+        <v>8459</v>
       </c>
       <c r="I20" t="s">
-        <v>8038</v>
+        <v>8463</v>
       </c>
       <c r="J20" t="s">
-        <v>8044</v>
+        <v>8463</v>
       </c>
       <c r="K20" t="s">
-        <v>8062</v>
+        <v>8459</v>
       </c>
       <c r="L20" t="s">
-        <v>8070</v>
+        <v>8463</v>
       </c>
       <c r="M20" t="s">
-        <v>8090</v>
+        <v>8459</v>
       </c>
       <c r="N20" t="s">
-        <v>8111</v>
+        <v>8459</v>
       </c>
       <c r="O20" t="s">
-        <v>8133</v>
+        <v>8459</v>
       </c>
       <c r="P20" t="s">
-        <v>8156</v>
+        <v>8459</v>
       </c>
       <c r="Q20" t="s">
-        <v>8179</v>
+        <v>8459</v>
       </c>
       <c r="R20" t="s">
-        <v>8190</v>
+        <v>8459</v>
       </c>
       <c r="S20" t="s">
-        <v>8199</v>
+        <v>8463</v>
       </c>
       <c r="T20" t="s">
-        <v>8217</v>
+        <v>8459</v>
       </c>
       <c r="U20" t="s">
-        <v>8237</v>
+        <v>8459</v>
       </c>
       <c r="V20" t="s">
-        <v>8258</v>
+        <v>8459</v>
       </c>
       <c r="W20" t="s">
-        <v>8280</v>
+        <v>8459</v>
       </c>
       <c r="X20" t="s">
-        <v>8302</v>
+        <v>8459</v>
       </c>
       <c r="Y20" t="s">
-        <v>8325</v>
+        <v>8459</v>
       </c>
       <c r="Z20" t="s">
-        <v>8346</v>
+        <v>8459</v>
       </c>
       <c r="AA20" t="s">
-        <v>8355</v>
+        <v>8463</v>
       </c>
       <c r="AB20" t="s">
-        <v>8361</v>
+        <v>8463</v>
       </c>
       <c r="AC20" t="s">
-        <v>8381</v>
+        <v>8459</v>
       </c>
       <c r="AD20" t="s">
-        <v>8404</v>
+        <v>8459</v>
       </c>
       <c r="AE20" t="s">
-        <v>8413</v>
+        <v>8463</v>
       </c>
       <c r="AF20" t="s">
-        <v>8433</v>
+        <v>8459</v>
       </c>
       <c r="AG20" t="s">
-        <v>8456</v>
+        <v>8459</v>
       </c>
       <c r="AH20" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI20" t="s">
         <v>8463</v>
@@ -30141,100 +30141,100 @@
         <v>2011</v>
       </c>
       <c r="C21" t="s">
-        <v>7949</v>
+        <v>8463</v>
       </c>
       <c r="D21" t="s">
-        <v>7968</v>
+        <v>8463</v>
       </c>
       <c r="E21" t="s">
-        <v>7983</v>
+        <v>8463</v>
       </c>
       <c r="F21" t="s">
-        <v>7990</v>
+        <v>8463</v>
       </c>
       <c r="G21" t="s">
-        <v>8009</v>
+        <v>8463</v>
       </c>
       <c r="H21" t="s">
-        <v>8030</v>
+        <v>8459</v>
       </c>
       <c r="I21" t="s">
-        <v>8038</v>
+        <v>8463</v>
       </c>
       <c r="J21" t="s">
-        <v>8044</v>
+        <v>8463</v>
       </c>
       <c r="K21" t="s">
-        <v>8063</v>
+        <v>8463</v>
       </c>
       <c r="L21" t="s">
-        <v>8070</v>
+        <v>8463</v>
       </c>
       <c r="M21" t="s">
-        <v>8091</v>
+        <v>8459</v>
       </c>
       <c r="N21" t="s">
-        <v>8112</v>
+        <v>8459</v>
       </c>
       <c r="O21" t="s">
-        <v>8134</v>
+        <v>8459</v>
       </c>
       <c r="P21" t="s">
-        <v>8157</v>
+        <v>8459</v>
       </c>
       <c r="Q21" t="s">
-        <v>8180</v>
+        <v>8459</v>
       </c>
       <c r="R21" t="s">
-        <v>8191</v>
+        <v>8459</v>
       </c>
       <c r="S21" t="s">
-        <v>8199</v>
+        <v>8463</v>
       </c>
       <c r="T21" t="s">
-        <v>8218</v>
+        <v>8463</v>
       </c>
       <c r="U21" t="s">
-        <v>8238</v>
+        <v>8463</v>
       </c>
       <c r="V21" t="s">
-        <v>8259</v>
+        <v>8463</v>
       </c>
       <c r="W21" t="s">
-        <v>8281</v>
+        <v>8459</v>
       </c>
       <c r="X21" t="s">
-        <v>8303</v>
+        <v>8459</v>
       </c>
       <c r="Y21" t="s">
-        <v>8326</v>
+        <v>8459</v>
       </c>
       <c r="Z21" t="s">
-        <v>8347</v>
+        <v>8463</v>
       </c>
       <c r="AA21" t="s">
-        <v>8355</v>
+        <v>8463</v>
       </c>
       <c r="AB21" t="s">
-        <v>8361</v>
+        <v>8463</v>
       </c>
       <c r="AC21" t="s">
-        <v>8382</v>
+        <v>8459</v>
       </c>
       <c r="AD21" t="s">
-        <v>8405</v>
+        <v>8459</v>
       </c>
       <c r="AE21" t="s">
-        <v>8413</v>
+        <v>8463</v>
       </c>
       <c r="AF21" t="s">
-        <v>8434</v>
+        <v>8459</v>
       </c>
       <c r="AG21" t="s">
-        <v>8457</v>
+        <v>8459</v>
       </c>
       <c r="AH21" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI21" t="s">
         <v>8463</v>
@@ -30248,100 +30248,100 @@
         <v>2009</v>
       </c>
       <c r="C22" t="s">
-        <v>7949</v>
+        <v>8463</v>
       </c>
       <c r="D22" t="s">
-        <v>7968</v>
+        <v>8463</v>
       </c>
       <c r="E22" t="s">
-        <v>7983</v>
+        <v>8463</v>
       </c>
       <c r="F22" t="s">
-        <v>7990</v>
+        <v>8463</v>
       </c>
       <c r="G22" t="s">
-        <v>8009</v>
+        <v>8463</v>
       </c>
       <c r="H22" t="s">
-        <v>8031</v>
+        <v>8463</v>
       </c>
       <c r="I22" t="s">
-        <v>8038</v>
+        <v>8463</v>
       </c>
       <c r="J22" t="s">
-        <v>8044</v>
+        <v>8463</v>
       </c>
       <c r="K22" t="s">
-        <v>8063</v>
+        <v>8463</v>
       </c>
       <c r="L22" t="s">
-        <v>8070</v>
+        <v>8463</v>
       </c>
       <c r="M22" t="s">
-        <v>8092</v>
+        <v>8459</v>
       </c>
       <c r="N22" t="s">
-        <v>8113</v>
+        <v>8459</v>
       </c>
       <c r="O22" t="s">
-        <v>8135</v>
+        <v>8459</v>
       </c>
       <c r="P22" t="s">
-        <v>8158</v>
+        <v>8459</v>
       </c>
       <c r="Q22" t="s">
-        <v>8181</v>
+        <v>8459</v>
       </c>
       <c r="R22" t="s">
-        <v>8192</v>
+        <v>8459</v>
       </c>
       <c r="S22" t="s">
-        <v>8199</v>
+        <v>8463</v>
       </c>
       <c r="T22" t="s">
-        <v>8218</v>
+        <v>8463</v>
       </c>
       <c r="U22" t="s">
-        <v>8238</v>
+        <v>8463</v>
       </c>
       <c r="V22" t="s">
-        <v>8260</v>
+        <v>8459</v>
       </c>
       <c r="W22" t="s">
-        <v>8282</v>
+        <v>8459</v>
       </c>
       <c r="X22" t="s">
-        <v>8304</v>
+        <v>8459</v>
       </c>
       <c r="Y22" t="s">
-        <v>8327</v>
+        <v>8459</v>
       </c>
       <c r="Z22" t="s">
-        <v>8348</v>
+        <v>8459</v>
       </c>
       <c r="AA22" t="s">
-        <v>8355</v>
+        <v>8463</v>
       </c>
       <c r="AB22" t="s">
-        <v>8361</v>
+        <v>8463</v>
       </c>
       <c r="AC22" t="s">
-        <v>8383</v>
+        <v>8459</v>
       </c>
       <c r="AD22" t="s">
-        <v>8406</v>
+        <v>8459</v>
       </c>
       <c r="AE22" t="s">
-        <v>8413</v>
+        <v>8463</v>
       </c>
       <c r="AF22" t="s">
-        <v>8435</v>
+        <v>8459</v>
       </c>
       <c r="AG22" t="s">
-        <v>8458</v>
+        <v>8459</v>
       </c>
       <c r="AH22" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI22" t="s">
         <v>8463</v>
@@ -30355,100 +30355,100 @@
         <v>2013</v>
       </c>
       <c r="C23" t="s">
-        <v>7949</v>
+        <v>8463</v>
       </c>
       <c r="D23" t="s">
-        <v>7969</v>
+        <v>8459</v>
       </c>
       <c r="E23" t="s">
-        <v>7984</v>
+        <v>8459</v>
       </c>
       <c r="F23" t="s">
-        <v>7990</v>
+        <v>8463</v>
       </c>
       <c r="G23" t="s">
-        <v>8010</v>
+        <v>8459</v>
       </c>
       <c r="H23" t="s">
-        <v>8032</v>
+        <v>8459</v>
       </c>
       <c r="I23" t="s">
-        <v>8038</v>
+        <v>8463</v>
       </c>
       <c r="J23" t="s">
-        <v>8044</v>
+        <v>8463</v>
       </c>
       <c r="K23" t="s">
-        <v>8064</v>
+        <v>8459</v>
       </c>
       <c r="L23" t="s">
-        <v>8070</v>
+        <v>8463</v>
       </c>
       <c r="M23" t="s">
-        <v>8093</v>
+        <v>8459</v>
       </c>
       <c r="N23" t="s">
-        <v>8114</v>
+        <v>8459</v>
       </c>
       <c r="O23" t="s">
-        <v>8136</v>
+        <v>8459</v>
       </c>
       <c r="P23" t="s">
-        <v>8159</v>
+        <v>8459</v>
       </c>
       <c r="Q23" t="s">
-        <v>8182</v>
+        <v>8459</v>
       </c>
       <c r="R23" t="s">
-        <v>8193</v>
+        <v>8463</v>
       </c>
       <c r="S23" t="s">
-        <v>8199</v>
+        <v>8463</v>
       </c>
       <c r="T23" t="s">
-        <v>8219</v>
+        <v>8459</v>
       </c>
       <c r="U23" t="s">
-        <v>8239</v>
+        <v>8459</v>
       </c>
       <c r="V23" t="s">
-        <v>8261</v>
+        <v>8459</v>
       </c>
       <c r="W23" t="s">
-        <v>8283</v>
+        <v>8459</v>
       </c>
       <c r="X23" t="s">
-        <v>8305</v>
+        <v>8459</v>
       </c>
       <c r="Y23" t="s">
-        <v>8328</v>
+        <v>8459</v>
       </c>
       <c r="Z23" t="s">
-        <v>8349</v>
+        <v>8459</v>
       </c>
       <c r="AA23" t="s">
-        <v>8355</v>
+        <v>8463</v>
       </c>
       <c r="AB23" t="s">
-        <v>8361</v>
+        <v>8463</v>
       </c>
       <c r="AC23" t="s">
-        <v>8384</v>
+        <v>8459</v>
       </c>
       <c r="AD23" t="s">
-        <v>8407</v>
+        <v>8459</v>
       </c>
       <c r="AE23" t="s">
-        <v>8413</v>
+        <v>8463</v>
       </c>
       <c r="AF23" t="s">
-        <v>8436</v>
+        <v>8459</v>
       </c>
       <c r="AG23" t="s">
         <v>8459</v>
       </c>
       <c r="AH23" t="s">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="AI23" t="s">
         <v>8463</v>

--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15890" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19068" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>

--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19068" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22246" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>

--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22246" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31780" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>

--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31780" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41314" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>

--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41314" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47670" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>

--- a/output/data_reports/ceq_data_availability.xlsx
+++ b/output/data_reports/ceq_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47670" uniqueCount="8464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54026" uniqueCount="8464">
   <si>
     <t>country</t>
   </si>
